--- a/data/hex_xlsx/SAGCV.HE.xlsx
+++ b/data/hex_xlsx/SAGCV.HE.xlsx
@@ -1128,7 +1128,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="[&gt;=100]#,###0.0\%;[&lt;=-100]-#,###0.0\%;#,###0.0\%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1171,6 +1171,12 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FFF5475B"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1242,7 +1248,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1306,16 +1312,19 @@
     <xf borderId="3" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -2710,15 +2719,33 @@
       <c r="N32" s="17">
         <v>41.31</v>
       </c>
-      <c r="O32" s="16"/>
+      <c r="O32" s="21">
+        <f>SUM(O33:O37)</f>
+        <v>141.93</v>
+      </c>
       <c r="P32" s="17">
         <v>19.2</v>
       </c>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
+      <c r="Q32" s="21">
+        <f t="shared" ref="Q32:U32" si="1">SUM(Q33:Q37)</f>
+        <v>142.69</v>
+      </c>
+      <c r="R32" s="21">
+        <f t="shared" si="1"/>
+        <v>132.48</v>
+      </c>
+      <c r="S32" s="21">
+        <f t="shared" si="1"/>
+        <v>128.84</v>
+      </c>
+      <c r="T32" s="21">
+        <f t="shared" si="1"/>
+        <v>119.78</v>
+      </c>
+      <c r="U32" s="21">
+        <f t="shared" si="1"/>
+        <v>115.5</v>
+      </c>
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
@@ -3113,7 +3140,7 @@
       <c r="H41" s="16"/>
       <c r="I41" s="16"/>
       <c r="J41" s="16"/>
-      <c r="K41" s="21">
+      <c r="K41" s="22">
         <v>0.0</v>
       </c>
       <c r="L41" s="16"/>
@@ -3424,40 +3451,40 @@
       <c r="A49" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="23">
         <v>16.18</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="23">
         <v>20.26</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="23">
         <v>36.07</v>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="24">
         <v>-2.6</v>
       </c>
       <c r="F49" s="19">
         <v>113.13</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="25">
         <v>-133.67</v>
       </c>
-      <c r="H49" s="23">
+      <c r="H49" s="24">
         <v>-23.36</v>
       </c>
-      <c r="I49" s="23">
+      <c r="I49" s="24">
         <v>-42.84</v>
       </c>
-      <c r="J49" s="22">
+      <c r="J49" s="23">
         <v>53.23</v>
       </c>
-      <c r="K49" s="23">
+      <c r="K49" s="24">
         <v>-54.92</v>
       </c>
-      <c r="L49" s="22">
+      <c r="L49" s="23">
         <v>39.19</v>
       </c>
-      <c r="M49" s="23">
+      <c r="M49" s="24">
         <v>-8.73</v>
       </c>
       <c r="N49" s="19">
@@ -3469,19 +3496,19 @@
       <c r="P49" s="19">
         <v>119.11</v>
       </c>
-      <c r="Q49" s="22">
+      <c r="Q49" s="23">
         <v>59.5</v>
       </c>
-      <c r="R49" s="23">
+      <c r="R49" s="24">
         <v>-34.46</v>
       </c>
-      <c r="S49" s="22">
+      <c r="S49" s="23">
         <v>8.23</v>
       </c>
-      <c r="T49" s="22">
+      <c r="T49" s="23">
         <v>4.05</v>
       </c>
-      <c r="U49" s="22">
+      <c r="U49" s="23">
         <v>60.67</v>
       </c>
     </row>
@@ -3761,7 +3788,7 @@
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
-      <c r="N56" s="21">
+      <c r="N56" s="22">
         <v>0.0</v>
       </c>
       <c r="O56" s="16"/>
@@ -4135,64 +4162,64 @@
       <c r="A66" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B66" s="22">
+      <c r="B66" s="23">
         <v>36.66</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="23">
         <v>19.88</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D66" s="23">
         <v>32.19</v>
       </c>
-      <c r="E66" s="22">
+      <c r="E66" s="23">
         <v>14.14</v>
       </c>
-      <c r="F66" s="22">
+      <c r="F66" s="23">
         <v>57.26</v>
       </c>
-      <c r="G66" s="22">
+      <c r="G66" s="23">
         <v>23.37</v>
       </c>
-      <c r="H66" s="22">
+      <c r="H66" s="23">
         <v>16.46</v>
       </c>
-      <c r="I66" s="22">
+      <c r="I66" s="23">
         <v>26.17</v>
       </c>
-      <c r="J66" s="22">
+      <c r="J66" s="23">
         <v>31.37</v>
       </c>
-      <c r="K66" s="22">
+      <c r="K66" s="23">
         <v>27.27</v>
       </c>
-      <c r="L66" s="22">
+      <c r="L66" s="23">
         <v>43.88</v>
       </c>
-      <c r="M66" s="22">
+      <c r="M66" s="23">
         <v>26.0</v>
       </c>
-      <c r="N66" s="22">
+      <c r="N66" s="23">
         <v>36.4</v>
       </c>
-      <c r="O66" s="22">
+      <c r="O66" s="23">
         <v>40.29</v>
       </c>
-      <c r="P66" s="22">
+      <c r="P66" s="23">
         <v>28.29</v>
       </c>
-      <c r="Q66" s="22">
+      <c r="Q66" s="23">
         <v>26.91</v>
       </c>
-      <c r="R66" s="22">
+      <c r="R66" s="23">
         <v>14.69</v>
       </c>
-      <c r="S66" s="22">
+      <c r="S66" s="23">
         <v>26.44</v>
       </c>
-      <c r="T66" s="22">
+      <c r="T66" s="23">
         <v>25.99</v>
       </c>
-      <c r="U66" s="22">
+      <c r="U66" s="23">
         <v>21.49</v>
       </c>
     </row>
@@ -4212,7 +4239,7 @@
       <c r="G67" s="20">
         <v>-0.01</v>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="22">
         <v>0.0</v>
       </c>
       <c r="I67" s="16"/>
@@ -4239,40 +4266,40 @@
       <c r="A68" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B68" s="22">
+      <c r="B68" s="23">
         <v>52.82</v>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="23">
         <v>40.14</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="23">
         <v>68.26</v>
       </c>
-      <c r="E68" s="22">
+      <c r="E68" s="23">
         <v>11.55</v>
       </c>
       <c r="F68" s="19">
         <v>170.39</v>
       </c>
-      <c r="G68" s="24">
+      <c r="G68" s="25">
         <v>-110.31</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="24">
         <v>-6.9</v>
       </c>
-      <c r="I68" s="23">
+      <c r="I68" s="24">
         <v>-16.67</v>
       </c>
-      <c r="J68" s="22">
+      <c r="J68" s="23">
         <v>84.6</v>
       </c>
-      <c r="K68" s="23">
+      <c r="K68" s="24">
         <v>-27.65</v>
       </c>
-      <c r="L68" s="22">
+      <c r="L68" s="23">
         <v>83.06</v>
       </c>
-      <c r="M68" s="22">
+      <c r="M68" s="23">
         <v>17.27</v>
       </c>
       <c r="N68" s="19">
@@ -4284,19 +4311,19 @@
       <c r="P68" s="19">
         <v>147.39</v>
       </c>
-      <c r="Q68" s="22">
+      <c r="Q68" s="23">
         <v>86.41</v>
       </c>
-      <c r="R68" s="23">
+      <c r="R68" s="24">
         <v>-19.77</v>
       </c>
-      <c r="S68" s="22">
+      <c r="S68" s="23">
         <v>34.67</v>
       </c>
-      <c r="T68" s="22">
+      <c r="T68" s="23">
         <v>30.04</v>
       </c>
-      <c r="U68" s="22">
+      <c r="U68" s="23">
         <v>82.16</v>
       </c>
     </row>
@@ -4554,64 +4581,64 @@
       <c r="A75" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="23">
         <v>11.47</v>
       </c>
-      <c r="C75" s="22">
+      <c r="C75" s="23">
         <v>10.38</v>
       </c>
-      <c r="D75" s="22">
+      <c r="D75" s="23">
         <v>13.11</v>
       </c>
-      <c r="E75" s="22">
+      <c r="E75" s="23">
         <v>1.1</v>
       </c>
-      <c r="F75" s="22">
+      <c r="F75" s="23">
         <v>38.64</v>
       </c>
-      <c r="G75" s="23">
+      <c r="G75" s="24">
         <v>-21.11</v>
       </c>
-      <c r="H75" s="23">
+      <c r="H75" s="24">
         <v>-0.24</v>
       </c>
-      <c r="I75" s="23">
+      <c r="I75" s="24">
         <v>-2.18</v>
       </c>
-      <c r="J75" s="22">
+      <c r="J75" s="23">
         <v>17.72</v>
       </c>
-      <c r="K75" s="23">
+      <c r="K75" s="24">
         <v>-4.88</v>
       </c>
-      <c r="L75" s="22">
+      <c r="L75" s="23">
         <v>17.64</v>
       </c>
-      <c r="M75" s="22">
+      <c r="M75" s="23">
         <v>5.07</v>
       </c>
-      <c r="N75" s="22">
+      <c r="N75" s="23">
         <v>56.47</v>
       </c>
-      <c r="O75" s="22">
+      <c r="O75" s="23">
         <v>42.28</v>
       </c>
-      <c r="P75" s="22">
+      <c r="P75" s="23">
         <v>38.49</v>
       </c>
-      <c r="Q75" s="22">
+      <c r="Q75" s="23">
         <v>22.69</v>
       </c>
-      <c r="R75" s="23">
+      <c r="R75" s="24">
         <v>-4.88</v>
       </c>
-      <c r="S75" s="22">
+      <c r="S75" s="23">
         <v>9.29</v>
       </c>
-      <c r="T75" s="22">
+      <c r="T75" s="23">
         <v>8.07</v>
       </c>
-      <c r="U75" s="22">
+      <c r="U75" s="23">
         <v>21.8</v>
       </c>
     </row>
@@ -4634,7 +4661,7 @@
       <c r="N76" s="16"/>
       <c r="O76" s="16"/>
       <c r="P76" s="16"/>
-      <c r="Q76" s="21">
+      <c r="Q76" s="22">
         <v>0.0</v>
       </c>
       <c r="R76" s="16"/>
@@ -4646,40 +4673,40 @@
       <c r="A77" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="22">
+      <c r="B77" s="23">
         <v>41.35</v>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="23">
         <v>29.76</v>
       </c>
-      <c r="D77" s="22">
+      <c r="D77" s="23">
         <v>55.15</v>
       </c>
-      <c r="E77" s="22">
+      <c r="E77" s="23">
         <v>10.45</v>
       </c>
       <c r="F77" s="19">
         <v>131.75</v>
       </c>
-      <c r="G77" s="23">
+      <c r="G77" s="24">
         <v>-89.21</v>
       </c>
-      <c r="H77" s="23">
+      <c r="H77" s="24">
         <v>-6.66</v>
       </c>
-      <c r="I77" s="23">
+      <c r="I77" s="24">
         <v>-14.49</v>
       </c>
-      <c r="J77" s="22">
+      <c r="J77" s="23">
         <v>66.88</v>
       </c>
-      <c r="K77" s="23">
+      <c r="K77" s="24">
         <v>-22.77</v>
       </c>
-      <c r="L77" s="22">
+      <c r="L77" s="23">
         <v>65.43</v>
       </c>
-      <c r="M77" s="22">
+      <c r="M77" s="23">
         <v>12.2</v>
       </c>
       <c r="N77" s="19">
@@ -4691,19 +4718,19 @@
       <c r="P77" s="19">
         <v>108.9</v>
       </c>
-      <c r="Q77" s="22">
+      <c r="Q77" s="23">
         <v>63.72</v>
       </c>
-      <c r="R77" s="23">
+      <c r="R77" s="24">
         <v>-14.88</v>
       </c>
-      <c r="S77" s="22">
+      <c r="S77" s="23">
         <v>25.38</v>
       </c>
-      <c r="T77" s="22">
+      <c r="T77" s="23">
         <v>21.97</v>
       </c>
-      <c r="U77" s="22">
+      <c r="U77" s="23">
         <v>60.35</v>
       </c>
     </row>
@@ -4724,12 +4751,12 @@
       <c r="L78" s="16"/>
       <c r="M78" s="16"/>
       <c r="N78" s="16"/>
-      <c r="O78" s="21">
+      <c r="O78" s="22">
         <v>0.0</v>
       </c>
       <c r="P78" s="16"/>
       <c r="Q78" s="16"/>
-      <c r="R78" s="21">
+      <c r="R78" s="22">
         <v>0.0</v>
       </c>
       <c r="S78" s="16"/>
@@ -4740,40 +4767,40 @@
       <c r="A79" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="22">
+      <c r="B79" s="23">
         <v>41.35</v>
       </c>
-      <c r="C79" s="22">
+      <c r="C79" s="23">
         <v>29.76</v>
       </c>
-      <c r="D79" s="22">
+      <c r="D79" s="23">
         <v>55.15</v>
       </c>
-      <c r="E79" s="22">
+      <c r="E79" s="23">
         <v>10.45</v>
       </c>
       <c r="F79" s="19">
         <v>131.75</v>
       </c>
-      <c r="G79" s="23">
+      <c r="G79" s="24">
         <v>-89.21</v>
       </c>
-      <c r="H79" s="23">
+      <c r="H79" s="24">
         <v>-6.66</v>
       </c>
-      <c r="I79" s="23">
+      <c r="I79" s="24">
         <v>-14.49</v>
       </c>
-      <c r="J79" s="22">
+      <c r="J79" s="23">
         <v>66.88</v>
       </c>
-      <c r="K79" s="23">
+      <c r="K79" s="24">
         <v>-22.77</v>
       </c>
-      <c r="L79" s="22">
+      <c r="L79" s="23">
         <v>65.43</v>
       </c>
-      <c r="M79" s="22">
+      <c r="M79" s="23">
         <v>12.2</v>
       </c>
       <c r="N79" s="19">
@@ -4785,19 +4812,19 @@
       <c r="P79" s="19">
         <v>108.9</v>
       </c>
-      <c r="Q79" s="22">
+      <c r="Q79" s="23">
         <v>63.72</v>
       </c>
-      <c r="R79" s="23">
+      <c r="R79" s="24">
         <v>-14.88</v>
       </c>
-      <c r="S79" s="22">
+      <c r="S79" s="23">
         <v>25.38</v>
       </c>
-      <c r="T79" s="22">
+      <c r="T79" s="23">
         <v>21.97</v>
       </c>
-      <c r="U79" s="22">
+      <c r="U79" s="23">
         <v>60.35</v>
       </c>
     </row>
@@ -4822,7 +4849,7 @@
         <v>0.0</v>
       </c>
       <c r="P80" s="16"/>
-      <c r="Q80" s="21">
+      <c r="Q80" s="22">
         <v>0.0</v>
       </c>
       <c r="R80" s="16">
@@ -4836,40 +4863,40 @@
       <c r="A81" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="22">
+      <c r="B81" s="23">
         <v>41.35</v>
       </c>
-      <c r="C81" s="22">
+      <c r="C81" s="23">
         <v>29.76</v>
       </c>
-      <c r="D81" s="22">
+      <c r="D81" s="23">
         <v>55.15</v>
       </c>
-      <c r="E81" s="22">
+      <c r="E81" s="23">
         <v>10.45</v>
       </c>
       <c r="F81" s="19">
         <v>131.75</v>
       </c>
-      <c r="G81" s="23">
+      <c r="G81" s="24">
         <v>-89.21</v>
       </c>
-      <c r="H81" s="23">
+      <c r="H81" s="24">
         <v>-6.66</v>
       </c>
-      <c r="I81" s="23">
+      <c r="I81" s="24">
         <v>-14.49</v>
       </c>
-      <c r="J81" s="22">
+      <c r="J81" s="23">
         <v>66.88</v>
       </c>
-      <c r="K81" s="23">
+      <c r="K81" s="24">
         <v>-22.77</v>
       </c>
-      <c r="L81" s="22">
+      <c r="L81" s="23">
         <v>65.43</v>
       </c>
-      <c r="M81" s="22">
+      <c r="M81" s="23">
         <v>12.2</v>
       </c>
       <c r="N81" s="19">
@@ -4881,19 +4908,19 @@
       <c r="P81" s="19">
         <v>108.9</v>
       </c>
-      <c r="Q81" s="22">
+      <c r="Q81" s="23">
         <v>63.71</v>
       </c>
-      <c r="R81" s="23">
+      <c r="R81" s="24">
         <v>-14.88</v>
       </c>
-      <c r="S81" s="22">
+      <c r="S81" s="23">
         <v>25.38</v>
       </c>
-      <c r="T81" s="22">
+      <c r="T81" s="23">
         <v>21.97</v>
       </c>
-      <c r="U81" s="22">
+      <c r="U81" s="23">
         <v>60.35</v>
       </c>
     </row>
@@ -4914,14 +4941,14 @@
       <c r="L82" s="16"/>
       <c r="M82" s="16"/>
       <c r="N82" s="16"/>
-      <c r="O82" s="21">
+      <c r="O82" s="22">
         <v>0.0</v>
       </c>
       <c r="P82" s="16"/>
       <c r="Q82" s="16">
         <v>0.0</v>
       </c>
-      <c r="R82" s="21">
+      <c r="R82" s="22">
         <v>0.0</v>
       </c>
       <c r="S82" s="16"/>
@@ -4932,40 +4959,40 @@
       <c r="A83" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B83" s="22">
+      <c r="B83" s="23">
         <v>41.35</v>
       </c>
-      <c r="C83" s="22">
+      <c r="C83" s="23">
         <v>29.76</v>
       </c>
-      <c r="D83" s="22">
+      <c r="D83" s="23">
         <v>55.15</v>
       </c>
-      <c r="E83" s="22">
+      <c r="E83" s="23">
         <v>10.45</v>
       </c>
       <c r="F83" s="19">
         <v>131.75</v>
       </c>
-      <c r="G83" s="23">
+      <c r="G83" s="24">
         <v>-89.21</v>
       </c>
-      <c r="H83" s="23">
+      <c r="H83" s="24">
         <v>-6.66</v>
       </c>
-      <c r="I83" s="23">
+      <c r="I83" s="24">
         <v>-14.49</v>
       </c>
-      <c r="J83" s="22">
+      <c r="J83" s="23">
         <v>66.88</v>
       </c>
-      <c r="K83" s="23">
+      <c r="K83" s="24">
         <v>-22.77</v>
       </c>
-      <c r="L83" s="22">
+      <c r="L83" s="23">
         <v>65.43</v>
       </c>
-      <c r="M83" s="22">
+      <c r="M83" s="23">
         <v>12.2</v>
       </c>
       <c r="N83" s="19">
@@ -4977,19 +5004,19 @@
       <c r="P83" s="19">
         <v>108.9</v>
       </c>
-      <c r="Q83" s="22">
+      <c r="Q83" s="23">
         <v>63.71</v>
       </c>
-      <c r="R83" s="23">
+      <c r="R83" s="24">
         <v>-14.88</v>
       </c>
-      <c r="S83" s="22">
+      <c r="S83" s="23">
         <v>25.38</v>
       </c>
-      <c r="T83" s="22">
+      <c r="T83" s="23">
         <v>21.97</v>
       </c>
-      <c r="U83" s="22">
+      <c r="U83" s="23">
         <v>60.35</v>
       </c>
     </row>
@@ -5018,14 +5045,14 @@
       <c r="L84" s="16"/>
       <c r="M84" s="16"/>
       <c r="N84" s="16"/>
-      <c r="O84" s="21">
+      <c r="O84" s="22">
         <v>0.0</v>
       </c>
       <c r="P84" s="16"/>
       <c r="Q84" s="16">
         <v>0.0</v>
       </c>
-      <c r="R84" s="21">
+      <c r="R84" s="22">
         <v>0.0</v>
       </c>
       <c r="S84" s="16"/>
@@ -5036,40 +5063,40 @@
       <c r="A85" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B85" s="22">
+      <c r="B85" s="23">
         <v>41.35</v>
       </c>
-      <c r="C85" s="22">
+      <c r="C85" s="23">
         <v>29.76</v>
       </c>
-      <c r="D85" s="22">
+      <c r="D85" s="23">
         <v>55.16</v>
       </c>
-      <c r="E85" s="22">
+      <c r="E85" s="23">
         <v>10.45</v>
       </c>
       <c r="F85" s="19">
         <v>131.74</v>
       </c>
-      <c r="G85" s="23">
+      <c r="G85" s="24">
         <v>-89.19</v>
       </c>
-      <c r="H85" s="23">
+      <c r="H85" s="24">
         <v>-6.66</v>
       </c>
-      <c r="I85" s="23">
+      <c r="I85" s="24">
         <v>-14.49</v>
       </c>
-      <c r="J85" s="22">
+      <c r="J85" s="23">
         <v>66.88</v>
       </c>
-      <c r="K85" s="23">
+      <c r="K85" s="24">
         <v>-22.77</v>
       </c>
-      <c r="L85" s="22">
+      <c r="L85" s="23">
         <v>65.43</v>
       </c>
-      <c r="M85" s="22">
+      <c r="M85" s="23">
         <v>12.2</v>
       </c>
       <c r="N85" s="19">
@@ -5081,19 +5108,19 @@
       <c r="P85" s="19">
         <v>108.9</v>
       </c>
-      <c r="Q85" s="22">
+      <c r="Q85" s="23">
         <v>63.71</v>
       </c>
-      <c r="R85" s="23">
+      <c r="R85" s="24">
         <v>-14.88</v>
       </c>
-      <c r="S85" s="22">
+      <c r="S85" s="23">
         <v>25.38</v>
       </c>
-      <c r="T85" s="22">
+      <c r="T85" s="23">
         <v>21.97</v>
       </c>
-      <c r="U85" s="22">
+      <c r="U85" s="23">
         <v>60.35</v>
       </c>
     </row>
@@ -8301,10 +8328,10 @@
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
-      <c r="M32" s="21">
+      <c r="M32" s="22">
         <v>0.0</v>
       </c>
-      <c r="N32" s="21">
+      <c r="N32" s="22">
         <v>0.0</v>
       </c>
       <c r="O32" s="16"/>
@@ -8499,10 +8526,10 @@
         <v>0.0</v>
       </c>
       <c r="J36" s="16"/>
-      <c r="K36" s="21">
+      <c r="K36" s="22">
         <v>0.0</v>
       </c>
-      <c r="L36" s="21">
+      <c r="L36" s="22">
         <v>0.0</v>
       </c>
       <c r="M36" s="16">
@@ -8510,7 +8537,7 @@
       </c>
       <c r="N36" s="16"/>
       <c r="O36" s="16"/>
-      <c r="P36" s="21">
+      <c r="P36" s="22">
         <v>0.0</v>
       </c>
       <c r="Q36" s="16"/>
@@ -8826,25 +8853,25 @@
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
       <c r="K43" s="16"/>
-      <c r="L43" s="25">
+      <c r="L43" s="26">
         <v>-232.5</v>
       </c>
-      <c r="M43" s="25">
+      <c r="M43" s="26">
         <v>-195.54</v>
       </c>
-      <c r="N43" s="25">
+      <c r="N43" s="26">
         <v>-174.32</v>
       </c>
-      <c r="O43" s="25">
+      <c r="O43" s="26">
         <v>-145.52</v>
       </c>
-      <c r="P43" s="25">
+      <c r="P43" s="26">
         <v>-142.86</v>
       </c>
-      <c r="Q43" s="25">
+      <c r="Q43" s="26">
         <v>-137.53</v>
       </c>
-      <c r="R43" s="25">
+      <c r="R43" s="26">
         <v>-137.36</v>
       </c>
       <c r="S43" s="16"/>
@@ -9016,7 +9043,7 @@
       <c r="J48" s="16"/>
       <c r="K48" s="16"/>
       <c r="L48" s="16"/>
-      <c r="M48" s="21">
+      <c r="M48" s="22">
         <v>0.0</v>
       </c>
       <c r="N48" s="16"/>
@@ -9087,25 +9114,25 @@
       <c r="I50" s="16"/>
       <c r="J50" s="16"/>
       <c r="K50" s="16"/>
-      <c r="L50" s="25">
+      <c r="L50" s="26">
         <v>-266.2</v>
       </c>
-      <c r="M50" s="25">
+      <c r="M50" s="26">
         <v>-226.54</v>
       </c>
-      <c r="N50" s="25">
+      <c r="N50" s="26">
         <v>-204.55</v>
       </c>
-      <c r="O50" s="25">
+      <c r="O50" s="26">
         <v>-173.19</v>
       </c>
-      <c r="P50" s="25">
+      <c r="P50" s="26">
         <v>-173.32</v>
       </c>
-      <c r="Q50" s="25">
+      <c r="Q50" s="26">
         <v>-170.91</v>
       </c>
-      <c r="R50" s="25">
+      <c r="R50" s="26">
         <v>-175.92</v>
       </c>
       <c r="S50" s="16"/>
@@ -9220,13 +9247,13 @@
       <c r="I53" s="16"/>
       <c r="J53" s="16"/>
       <c r="K53" s="16"/>
-      <c r="L53" s="25">
+      <c r="L53" s="26">
         <v>-169.2</v>
       </c>
-      <c r="M53" s="25">
+      <c r="M53" s="26">
         <v>-145.47</v>
       </c>
-      <c r="N53" s="25">
+      <c r="N53" s="26">
         <v>-132.19</v>
       </c>
       <c r="O53" s="16"/>
@@ -9417,7 +9444,7 @@
       <c r="J59" s="16"/>
       <c r="K59" s="16"/>
       <c r="L59" s="16"/>
-      <c r="M59" s="21">
+      <c r="M59" s="22">
         <v>0.0</v>
       </c>
       <c r="N59" s="16"/>
@@ -9446,22 +9473,22 @@
       <c r="L60" s="16"/>
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
-      <c r="O60" s="25">
+      <c r="O60" s="26">
         <v>-115.51</v>
       </c>
-      <c r="P60" s="25">
+      <c r="P60" s="26">
         <v>-117.56</v>
       </c>
-      <c r="Q60" s="25">
+      <c r="Q60" s="26">
         <v>-118.67</v>
       </c>
-      <c r="R60" s="25">
+      <c r="R60" s="26">
         <v>-125.2</v>
       </c>
-      <c r="S60" s="25">
+      <c r="S60" s="26">
         <v>-112.43</v>
       </c>
-      <c r="T60" s="25">
+      <c r="T60" s="26">
         <v>-109.75</v>
       </c>
       <c r="U60" s="16"/>
@@ -9691,13 +9718,13 @@
       <c r="P65" s="16"/>
       <c r="Q65" s="16"/>
       <c r="R65" s="16"/>
-      <c r="S65" s="25">
+      <c r="S65" s="26">
         <v>-270.72</v>
       </c>
-      <c r="T65" s="25">
+      <c r="T65" s="26">
         <v>-252.46</v>
       </c>
-      <c r="U65" s="25">
+      <c r="U65" s="26">
         <v>-240.39</v>
       </c>
     </row>
@@ -9756,7 +9783,7 @@
       <c r="M67" s="16">
         <v>0.0</v>
       </c>
-      <c r="N67" s="21">
+      <c r="N67" s="22">
         <v>0.0</v>
       </c>
       <c r="O67" s="16"/>
@@ -9849,7 +9876,7 @@
       <c r="J69" s="16"/>
       <c r="K69" s="16"/>
       <c r="L69" s="16"/>
-      <c r="M69" s="21">
+      <c r="M69" s="22">
         <v>0.0</v>
       </c>
       <c r="N69" s="16"/>
@@ -10193,7 +10220,7 @@
       <c r="E76" s="16"/>
       <c r="F76" s="16"/>
       <c r="G76" s="16"/>
-      <c r="H76" s="21">
+      <c r="H76" s="22">
         <v>0.0</v>
       </c>
       <c r="I76" s="16"/>
@@ -10202,10 +10229,10 @@
       <c r="L76" s="16">
         <v>0.0</v>
       </c>
-      <c r="M76" s="21">
+      <c r="M76" s="22">
         <v>0.0</v>
       </c>
-      <c r="N76" s="21">
+      <c r="N76" s="22">
         <v>0.0</v>
       </c>
       <c r="O76" s="16"/>
@@ -10549,7 +10576,7 @@
       <c r="J85" s="16"/>
       <c r="K85" s="16"/>
       <c r="L85" s="16"/>
-      <c r="M85" s="21">
+      <c r="M85" s="22">
         <v>0.0</v>
       </c>
       <c r="N85" s="16"/>
@@ -10671,7 +10698,7 @@
       <c r="G88" s="16"/>
       <c r="H88" s="16"/>
       <c r="I88" s="16"/>
-      <c r="J88" s="21">
+      <c r="J88" s="22">
         <v>0.0</v>
       </c>
       <c r="K88" s="16"/>
@@ -10684,7 +10711,7 @@
       </c>
       <c r="O88" s="16"/>
       <c r="P88" s="16"/>
-      <c r="Q88" s="21">
+      <c r="Q88" s="22">
         <v>0.0</v>
       </c>
       <c r="R88" s="16">
@@ -10974,7 +11001,7 @@
       <c r="Q95" s="16">
         <v>0.0</v>
       </c>
-      <c r="R95" s="21">
+      <c r="R95" s="22">
         <v>0.0</v>
       </c>
       <c r="S95" s="16"/>
@@ -10985,64 +11012,64 @@
       <c r="A96" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="B96" s="22">
+      <c r="B96" s="23">
         <v>25.29</v>
       </c>
-      <c r="C96" s="22">
+      <c r="C96" s="23">
         <v>46.51</v>
       </c>
-      <c r="D96" s="22">
+      <c r="D96" s="23">
         <v>73.41</v>
       </c>
-      <c r="E96" s="22">
+      <c r="E96" s="23">
         <v>84.94</v>
       </c>
-      <c r="F96" s="22">
+      <c r="F96" s="23">
         <v>79.53</v>
       </c>
-      <c r="G96" s="22">
+      <c r="G96" s="23">
         <v>95.36</v>
       </c>
-      <c r="H96" s="22">
+      <c r="H96" s="23">
         <v>16.33</v>
       </c>
-      <c r="I96" s="22">
+      <c r="I96" s="23">
         <v>18.26</v>
       </c>
-      <c r="J96" s="22">
+      <c r="J96" s="23">
         <v>22.15</v>
       </c>
-      <c r="K96" s="22">
+      <c r="K96" s="23">
         <v>15.2</v>
       </c>
-      <c r="L96" s="22">
+      <c r="L96" s="23">
         <v>22.86</v>
       </c>
-      <c r="M96" s="22">
+      <c r="M96" s="23">
         <v>20.57</v>
       </c>
-      <c r="N96" s="22">
+      <c r="N96" s="23">
         <v>21.13</v>
       </c>
-      <c r="O96" s="22">
+      <c r="O96" s="23">
         <v>19.33</v>
       </c>
-      <c r="P96" s="22">
+      <c r="P96" s="23">
         <v>21.82</v>
       </c>
-      <c r="Q96" s="22">
+      <c r="Q96" s="23">
         <v>23.09</v>
       </c>
-      <c r="R96" s="22">
+      <c r="R96" s="23">
         <v>21.4</v>
       </c>
-      <c r="S96" s="22">
+      <c r="S96" s="23">
         <v>25.22</v>
       </c>
-      <c r="T96" s="22">
+      <c r="T96" s="23">
         <v>27.89</v>
       </c>
-      <c r="U96" s="22">
+      <c r="U96" s="23">
         <v>32.93</v>
       </c>
     </row>
@@ -11674,16 +11701,16 @@
       <c r="L108" s="16"/>
       <c r="M108" s="16"/>
       <c r="N108" s="16"/>
-      <c r="O108" s="21">
+      <c r="O108" s="22">
         <v>0.0</v>
       </c>
-      <c r="P108" s="21">
+      <c r="P108" s="22">
         <v>0.0</v>
       </c>
       <c r="Q108" s="17">
         <v>0.01</v>
       </c>
-      <c r="R108" s="21">
+      <c r="R108" s="22">
         <v>0.0</v>
       </c>
       <c r="S108" s="16"/>
@@ -11770,15 +11797,15 @@
       </c>
       <c r="G110" s="16"/>
       <c r="H110" s="16"/>
-      <c r="I110" s="21">
+      <c r="I110" s="22">
         <v>0.0</v>
       </c>
       <c r="J110" s="16"/>
       <c r="K110" s="16"/>
-      <c r="L110" s="21">
+      <c r="L110" s="22">
         <v>0.0</v>
       </c>
-      <c r="M110" s="21">
+      <c r="M110" s="22">
         <v>0.0</v>
       </c>
       <c r="N110" s="16"/>
@@ -12104,7 +12131,7 @@
       <c r="N116" s="16"/>
       <c r="O116" s="16"/>
       <c r="P116" s="16"/>
-      <c r="Q116" s="25">
+      <c r="Q116" s="26">
         <v>-118.67</v>
       </c>
       <c r="R116" s="16"/>
@@ -12158,7 +12185,7 @@
       <c r="N118" s="16"/>
       <c r="O118" s="16"/>
       <c r="P118" s="16"/>
-      <c r="Q118" s="25">
+      <c r="Q118" s="26">
         <v>-170.91</v>
       </c>
       <c r="R118" s="16"/>
@@ -14253,13 +14280,13 @@
       <c r="F20" s="15">
         <v>1134.07</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <v>-368.65</v>
       </c>
       <c r="H20" s="20">
         <v>-41.04</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="26">
         <v>-124.51</v>
       </c>
       <c r="J20" s="15">
@@ -14271,7 +14298,7 @@
       <c r="L20" s="17">
         <v>60.23</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="26">
         <v>-475.49</v>
       </c>
       <c r="N20" s="17">
@@ -14421,64 +14448,64 @@
       <c r="A23" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <v>-3701.25</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="26">
         <v>-3753.02</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="26">
         <v>-3911.48</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="26">
         <v>-2797.13</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="26">
         <v>-3184.6</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="26">
         <v>-2033.46</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="26">
         <v>-3040.06</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="26">
         <v>-3215.23</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="26">
         <v>-3979.64</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="26">
         <v>-3028.08</v>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="26">
         <v>-5505.47</v>
       </c>
-      <c r="M23" s="25">
+      <c r="M23" s="26">
         <v>-4517.02</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="26">
         <v>-7492.63</v>
       </c>
-      <c r="O23" s="25">
+      <c r="O23" s="26">
         <v>-5075.51</v>
       </c>
-      <c r="P23" s="25">
+      <c r="P23" s="26">
         <v>-4553.68</v>
       </c>
-      <c r="Q23" s="25">
+      <c r="Q23" s="26">
         <v>-3348.99</v>
       </c>
-      <c r="R23" s="25">
+      <c r="R23" s="26">
         <v>-2253.64</v>
       </c>
-      <c r="S23" s="25">
+      <c r="S23" s="26">
         <v>-2503.02</v>
       </c>
-      <c r="T23" s="25">
+      <c r="T23" s="26">
         <v>-2968.76</v>
       </c>
-      <c r="U23" s="25">
+      <c r="U23" s="26">
         <v>-3095.68</v>
       </c>
     </row>
@@ -14950,7 +14977,7 @@
         <v>0.0</v>
       </c>
       <c r="L33" s="16"/>
-      <c r="M33" s="21">
+      <c r="M33" s="22">
         <v>0.0</v>
       </c>
       <c r="N33" s="16"/>
@@ -14972,22 +14999,22 @@
       <c r="C34" s="19">
         <v>304.3</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="23">
         <v>61.16</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="24">
         <v>-36.71</v>
       </c>
       <c r="F34" s="19">
         <v>1192.09</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="25">
         <v>-353.5</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="24">
         <v>-24.09</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="24">
         <v>-93.77</v>
       </c>
       <c r="J34" s="19">
@@ -14996,13 +15023,13 @@
       <c r="K34" s="19">
         <v>139.91</v>
       </c>
-      <c r="L34" s="22">
+      <c r="L34" s="23">
         <v>72.42</v>
       </c>
-      <c r="M34" s="24">
+      <c r="M34" s="25">
         <v>-465.13</v>
       </c>
-      <c r="N34" s="22">
+      <c r="N34" s="23">
         <v>62.12</v>
       </c>
       <c r="O34" s="19">
@@ -15014,16 +15041,16 @@
       <c r="Q34" s="19">
         <v>198.56</v>
       </c>
-      <c r="R34" s="22">
+      <c r="R34" s="23">
         <v>2.2</v>
       </c>
       <c r="S34" s="19">
         <v>147.03</v>
       </c>
-      <c r="T34" s="23">
+      <c r="T34" s="24">
         <v>-37.51</v>
       </c>
-      <c r="U34" s="23">
+      <c r="U34" s="24">
         <v>-8.42</v>
       </c>
     </row>
@@ -15064,7 +15091,7 @@
       <c r="L35" s="20">
         <v>-58.21</v>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="26">
         <v>-106.51</v>
       </c>
       <c r="N35" s="20">
@@ -15322,7 +15349,7 @@
         <v>0.0</v>
       </c>
       <c r="L41" s="16"/>
-      <c r="M41" s="21">
+      <c r="M41" s="22">
         <v>0.0</v>
       </c>
       <c r="N41" s="16"/>
@@ -15338,64 +15365,64 @@
       <c r="A42" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="B42" s="22">
+      <c r="B42" s="23">
         <v>2.89</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="24">
         <v>-33.2</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="24">
         <v>-33.94</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>14.98</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="24">
         <v>-9.48</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="23">
         <v>22.32</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="24">
         <v>-4.24</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="24">
         <v>-11.97</v>
       </c>
-      <c r="J42" s="23">
+      <c r="J42" s="24">
         <v>-16.26</v>
       </c>
-      <c r="K42" s="23">
+      <c r="K42" s="24">
         <v>-21.32</v>
       </c>
-      <c r="L42" s="23">
+      <c r="L42" s="24">
         <v>-56.77</v>
       </c>
-      <c r="M42" s="24">
+      <c r="M42" s="25">
         <v>-106.51</v>
       </c>
-      <c r="N42" s="23">
+      <c r="N42" s="24">
         <v>-39.73</v>
       </c>
-      <c r="O42" s="23">
+      <c r="O42" s="24">
         <v>-37.17</v>
       </c>
-      <c r="P42" s="23">
+      <c r="P42" s="24">
         <v>-69.07</v>
       </c>
-      <c r="Q42" s="23">
+      <c r="Q42" s="24">
         <v>-11.93</v>
       </c>
-      <c r="R42" s="23">
+      <c r="R42" s="24">
         <v>-17.54</v>
       </c>
-      <c r="S42" s="23">
+      <c r="S42" s="24">
         <v>-33.06</v>
       </c>
-      <c r="T42" s="23">
+      <c r="T42" s="24">
         <v>-21.73</v>
       </c>
-      <c r="U42" s="23">
+      <c r="U42" s="24">
         <v>-13.35</v>
       </c>
     </row>
@@ -15599,7 +15626,7 @@
       <c r="E47" s="16">
         <v>0.0</v>
       </c>
-      <c r="F47" s="25">
+      <c r="F47" s="26">
         <v>-709.48</v>
       </c>
       <c r="G47" s="20">
@@ -15611,7 +15638,7 @@
       <c r="I47" s="20">
         <v>-2.51</v>
       </c>
-      <c r="J47" s="25">
+      <c r="J47" s="26">
         <v>-419.85</v>
       </c>
       <c r="K47" s="20">
@@ -15624,7 +15651,7 @@
       <c r="P47" s="20">
         <v>-84.08</v>
       </c>
-      <c r="Q47" s="25">
+      <c r="Q47" s="26">
         <v>-148.15</v>
       </c>
       <c r="R47" s="16">
@@ -15739,64 +15766,64 @@
       <c r="A51" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="24">
         <v>-60.64</v>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="24">
         <v>-59.36</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="23">
         <v>17.01</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="24">
         <v>-59.48</v>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="25">
         <v>-735.71</v>
       </c>
       <c r="G51" s="19">
         <v>327.56</v>
       </c>
-      <c r="H51" s="22">
+      <c r="H51" s="23">
         <v>2.23</v>
       </c>
       <c r="I51" s="19">
         <v>107.65</v>
       </c>
-      <c r="J51" s="24">
+      <c r="J51" s="25">
         <v>-435.31</v>
       </c>
-      <c r="K51" s="23">
+      <c r="K51" s="24">
         <v>-66.6</v>
       </c>
-      <c r="L51" s="22">
+      <c r="L51" s="23">
         <v>3.71</v>
       </c>
       <c r="M51" s="19">
         <v>397.59</v>
       </c>
-      <c r="N51" s="23">
+      <c r="N51" s="24">
         <v>-15.17</v>
       </c>
-      <c r="O51" s="23">
+      <c r="O51" s="24">
         <v>-7.96</v>
       </c>
-      <c r="P51" s="24">
+      <c r="P51" s="25">
         <v>-113.93</v>
       </c>
-      <c r="Q51" s="24">
+      <c r="Q51" s="25">
         <v>-165.55</v>
       </c>
-      <c r="R51" s="23">
+      <c r="R51" s="24">
         <v>-0.37</v>
       </c>
-      <c r="S51" s="24">
+      <c r="S51" s="25">
         <v>-105.3</v>
       </c>
-      <c r="T51" s="22">
+      <c r="T51" s="23">
         <v>15.7</v>
       </c>
-      <c r="U51" s="22">
+      <c r="U51" s="23">
         <v>65.81</v>
       </c>
     </row>
@@ -15994,7 +16021,7 @@
       <c r="H55" s="16"/>
       <c r="I55" s="16"/>
       <c r="J55" s="16"/>
-      <c r="K55" s="21">
+      <c r="K55" s="22">
         <v>0.0</v>
       </c>
       <c r="L55" s="16"/>
@@ -16016,64 +16043,64 @@
       <c r="A56" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="B56" s="22">
+      <c r="B56" s="23">
         <v>91.9</v>
       </c>
       <c r="C56" s="19">
         <v>211.72</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="23">
         <v>44.24</v>
       </c>
-      <c r="E56" s="23">
+      <c r="E56" s="24">
         <v>-81.21</v>
       </c>
       <c r="F56" s="19">
         <v>446.9</v>
       </c>
-      <c r="G56" s="23">
+      <c r="G56" s="24">
         <v>-3.62</v>
       </c>
-      <c r="H56" s="23">
+      <c r="H56" s="24">
         <v>-26.1</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56" s="23">
         <v>1.92</v>
       </c>
-      <c r="J56" s="23">
+      <c r="J56" s="24">
         <v>-79.2</v>
       </c>
-      <c r="K56" s="22">
+      <c r="K56" s="23">
         <v>52.0</v>
       </c>
-      <c r="L56" s="22">
+      <c r="L56" s="23">
         <v>19.36</v>
       </c>
-      <c r="M56" s="24">
+      <c r="M56" s="25">
         <v>-174.05</v>
       </c>
-      <c r="N56" s="22">
+      <c r="N56" s="23">
         <v>7.21</v>
       </c>
       <c r="O56" s="19">
         <v>102.48</v>
       </c>
-      <c r="P56" s="22">
+      <c r="P56" s="23">
         <v>35.22</v>
       </c>
-      <c r="Q56" s="22">
+      <c r="Q56" s="23">
         <v>21.08</v>
       </c>
-      <c r="R56" s="23">
+      <c r="R56" s="24">
         <v>-15.71</v>
       </c>
-      <c r="S56" s="22">
+      <c r="S56" s="23">
         <v>8.65</v>
       </c>
-      <c r="T56" s="23">
+      <c r="T56" s="24">
         <v>-43.53</v>
       </c>
-      <c r="U56" s="22">
+      <c r="U56" s="23">
         <v>44.04</v>
       </c>
     </row>
@@ -17851,3186 +17878,3186 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>-322.03</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>-138.81</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>58.37</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>106.16</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>115.63</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>1042.49</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>757.7</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>602.82</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>713.22</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>927.05</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>1191.8</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>1263.88</v>
       </c>
-      <c r="N21" s="32"/>
-      <c r="O21" s="31">
+      <c r="N21" s="33"/>
+      <c r="O21" s="32">
         <v>207.9</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <v>239.7</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>269.16</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>443.16</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>376.74</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>517.62</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>447.24</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>337.21</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>302.53</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>171.86</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="32">
         <v>201.71</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="32">
         <v>165.92</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="32">
         <v>171.47</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="32">
         <v>122.26</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="34">
         <v>-28.2</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>261.76</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>460.6</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>519.67</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>620.44</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>906.83</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>906.08</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>987.53</v>
       </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="31">
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="32">
         <v>280.14</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>352.61</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="32">
         <v>403.66</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="32">
         <v>451.64</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="32">
         <v>392.84</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="32">
         <v>350.05</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="32">
         <v>295.49</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="32">
         <v>232.56</v>
       </c>
-      <c r="W22" s="31">
+      <c r="W22" s="32">
         <v>211.1</v>
       </c>
-      <c r="X22" s="31">
+      <c r="X22" s="32">
         <v>172.83</v>
       </c>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <v>281.0</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>396.03</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>346.02</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>395.11</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>474.32</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>208.69</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>398.42</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>292.58</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>545.68</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>444.09</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>611.26</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <v>765.29</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <v>959.47</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="32">
         <v>333.63</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="32">
         <v>295.03</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="32">
         <v>203.59</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>193.78</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>182.61</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>226.25</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>236.02</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>168.78</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>179.42</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>155.78</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="32">
         <v>162.49</v>
       </c>
-      <c r="Z24" s="31">
+      <c r="Z24" s="32">
         <v>173.91</v>
       </c>
-      <c r="AA24" s="31">
+      <c r="AA24" s="32">
         <v>163.24</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="32">
         <v>135.29</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <v>404.7</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>402.65</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>411.26</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>360.09</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>379.31</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>432.48</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>494.78</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>559.07</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>725.18</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>670.15</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>670.16</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="32">
         <v>539.5</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <v>404.96</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>226.0</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>212.27</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="32">
         <v>205.23</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="32">
         <v>214.63</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="32">
         <v>196.58</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="32">
         <v>189.79</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="32">
         <v>182.96</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="32">
         <v>165.85</v>
       </c>
-      <c r="W25" s="31">
+      <c r="W25" s="32">
         <v>174.28</v>
       </c>
-      <c r="X25" s="31">
+      <c r="X25" s="32">
         <v>163.39</v>
       </c>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="32"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <v>78.09</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>110.06</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>96.16</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>109.8</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>131.76</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>57.97</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>110.67</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>81.27</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>151.58</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>123.36</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>169.79</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>212.58</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>355.36</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>123.57</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>109.27</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="31">
         <v>75.41</v>
       </c>
-      <c r="R27" s="30">
+      <c r="R27" s="31">
         <v>71.77</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="31">
         <v>67.64</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="31">
         <v>83.8</v>
       </c>
-      <c r="U27" s="30">
+      <c r="U27" s="31">
         <v>87.42</v>
       </c>
-      <c r="V27" s="30">
+      <c r="V27" s="31">
         <v>62.51</v>
       </c>
-      <c r="W27" s="30">
+      <c r="W27" s="31">
         <v>66.45</v>
       </c>
-      <c r="X27" s="30">
+      <c r="X27" s="31">
         <v>57.7</v>
       </c>
-      <c r="Y27" s="30">
+      <c r="Y27" s="31">
         <v>60.18</v>
       </c>
-      <c r="Z27" s="30">
+      <c r="Z27" s="31">
         <v>64.41</v>
       </c>
-      <c r="AA27" s="30">
+      <c r="AA27" s="31">
         <v>60.46</v>
       </c>
-      <c r="AB27" s="30">
+      <c r="AB27" s="31">
         <v>50.11</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <v>112.45</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>111.88</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>114.26</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>100.03</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>105.37</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>120.13</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>137.44</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>155.3</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>222.38</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>213.8</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <v>221.24</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <v>185.64</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <v>149.98</v>
       </c>
-      <c r="O28" s="30">
+      <c r="O28" s="31">
         <v>83.7</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="31">
         <v>78.62</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="31">
         <v>76.01</v>
       </c>
-      <c r="R28" s="30">
+      <c r="R28" s="31">
         <v>79.49</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="31">
         <v>72.81</v>
       </c>
-      <c r="T28" s="30">
+      <c r="T28" s="31">
         <v>70.29</v>
       </c>
-      <c r="U28" s="30">
+      <c r="U28" s="31">
         <v>67.76</v>
       </c>
-      <c r="V28" s="30">
+      <c r="V28" s="31">
         <v>61.42</v>
       </c>
-      <c r="W28" s="30">
+      <c r="W28" s="31">
         <v>64.55</v>
       </c>
-      <c r="X28" s="30">
+      <c r="X28" s="31">
         <v>60.52</v>
       </c>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="35">
         <v>51.3</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>72.25</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>7.99</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>-16.92</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>241.07</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>-187.89</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>-8.75</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>-36.09</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>68.23</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>24.66</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>2.45</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>-76.25</v>
       </c>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34">
+      <c r="N30" s="35"/>
+      <c r="O30" s="35">
         <v>23.64</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>36.89</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>67.09</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>-5.99</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>46.81</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>-19.25</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="36">
         <v>-7.35</v>
       </c>
-      <c r="V30" s="35">
+      <c r="V30" s="36">
         <v>-16.75</v>
       </c>
-      <c r="W30" s="35">
+      <c r="W30" s="36">
         <v>-39.39</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="35">
         <v>22.83</v>
       </c>
-      <c r="Y30" s="35">
+      <c r="Y30" s="36">
         <v>-12.85</v>
       </c>
-      <c r="Z30" s="34">
+      <c r="Z30" s="35">
         <v>14.87</v>
       </c>
-      <c r="AA30" s="35">
+      <c r="AA30" s="36">
         <v>-7.13</v>
       </c>
-      <c r="AB30" s="34">
+      <c r="AB30" s="35">
         <v>42.11</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>85.96</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>60.36</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>42.66</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <v>34.69</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>54.82</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>0.75</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>15.9</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="36">
         <v>-9.3</v>
       </c>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34">
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35">
         <v>33.2</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>25.52</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <v>14.69</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="36">
         <v>-1.46</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="36">
         <v>-7.23</v>
       </c>
-      <c r="T31" s="35">
+      <c r="T31" s="36">
         <v>-12.86</v>
       </c>
-      <c r="U31" s="35">
+      <c r="U31" s="36">
         <v>-11.25</v>
       </c>
-      <c r="V31" s="35">
+      <c r="V31" s="36">
         <v>-6.97</v>
       </c>
-      <c r="W31" s="35">
+      <c r="W31" s="36">
         <v>-4.99</v>
       </c>
-      <c r="X31" s="34">
+      <c r="X31" s="35">
         <v>10.22</v>
       </c>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>10.6</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>7.17</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>1.72</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>18.6</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>0.0</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <v>0.0</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <v>4.63</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>11.74</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>3.14</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>7.35</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>3.85</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <v>8.15</v>
       </c>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34">
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35">
         <v>6.01</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="35">
         <v>5.1</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="35">
         <v>6.76</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="35">
         <v>6.62</v>
       </c>
-      <c r="T33" s="34">
+      <c r="T33" s="35">
         <v>7.24</v>
       </c>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34">
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35">
         <v>7.55</v>
       </c>
-      <c r="X33" s="34">
+      <c r="X33" s="35">
         <v>9.29</v>
       </c>
-      <c r="Y33" s="34">
+      <c r="Y33" s="35">
         <v>9.8</v>
       </c>
-      <c r="Z33" s="34">
+      <c r="Z33" s="35">
         <v>7.5</v>
       </c>
-      <c r="AA33" s="34">
+      <c r="AA33" s="35">
         <v>3.33</v>
       </c>
-      <c r="AB33" s="34">
+      <c r="AB33" s="35">
         <v>11.26</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <v>7.26</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>5.97</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>5.44</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>7.16</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>3.71</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>5.55</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <v>5.52</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="35">
         <v>6.45</v>
       </c>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34">
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35">
         <v>6.32</v>
       </c>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34">
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35">
         <v>7.51</v>
       </c>
-      <c r="X34" s="34">
+      <c r="X34" s="35">
         <v>8.12</v>
       </c>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35"/>
+      <c r="AA34" s="35"/>
+      <c r="AB34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="35">
         <v>10.6</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>7.17</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>1.72</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>18.6</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>0.0</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <v>0.0</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <v>4.63</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>11.74</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>3.14</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>7.35</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>3.85</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>8.15</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <v>3.86</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="35">
         <v>8.55</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="35">
         <v>7.48</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="35">
         <v>6.35</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="35">
         <v>8.4</v>
       </c>
-      <c r="S35" s="34">
+      <c r="S35" s="35">
         <v>8.24</v>
       </c>
-      <c r="T35" s="34">
+      <c r="T35" s="35">
         <v>9.0</v>
       </c>
-      <c r="U35" s="34">
+      <c r="U35" s="35">
         <v>6.02</v>
       </c>
-      <c r="V35" s="34">
+      <c r="V35" s="35">
         <v>8.18</v>
       </c>
-      <c r="W35" s="34">
+      <c r="W35" s="35">
         <v>7.55</v>
       </c>
-      <c r="X35" s="34">
+      <c r="X35" s="35">
         <v>9.29</v>
       </c>
-      <c r="Y35" s="34">
+      <c r="Y35" s="35">
         <v>9.8</v>
       </c>
-      <c r="Z35" s="34">
+      <c r="Z35" s="35">
         <v>7.5</v>
       </c>
-      <c r="AA35" s="34">
+      <c r="AA35" s="35">
         <v>3.33</v>
       </c>
-      <c r="AB35" s="34">
+      <c r="AB35" s="35">
         <v>11.26</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="35">
         <v>7.26</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>5.97</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>5.44</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>7.16</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>3.71</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>5.55</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <v>5.52</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="35">
         <v>6.45</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="35">
         <v>5.09</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="35">
         <v>5.85</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="35">
         <v>5.87</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <v>6.25</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="35">
         <v>5.93</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="35">
         <v>7.86</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="35">
         <v>7.86</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="35">
         <v>7.56</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="35">
         <v>7.91</v>
       </c>
-      <c r="S36" s="34">
+      <c r="S36" s="35">
         <v>7.76</v>
       </c>
-      <c r="T36" s="34">
+      <c r="T36" s="35">
         <v>7.91</v>
       </c>
-      <c r="U36" s="34">
+      <c r="U36" s="35">
         <v>8.0</v>
       </c>
-      <c r="V36" s="34">
+      <c r="V36" s="35">
         <v>8.45</v>
       </c>
-      <c r="W36" s="34">
+      <c r="W36" s="35">
         <v>7.51</v>
       </c>
-      <c r="X36" s="34">
+      <c r="X36" s="35">
         <v>8.12</v>
       </c>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="27" t="s">
         <v>330</v>
       </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="31">
         <v>0.26</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <v>0.37</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <v>0.32</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <v>0.45</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <v>0.54</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="31">
         <v>0.24</v>
       </c>
-      <c r="H38" s="30">
+      <c r="H38" s="31">
         <v>0.45</v>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="31">
         <v>0.34</v>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="31">
         <v>0.61</v>
       </c>
-      <c r="K38" s="30">
+      <c r="K38" s="31">
         <v>0.55</v>
       </c>
-      <c r="L38" s="30">
+      <c r="L38" s="31">
         <v>0.69</v>
       </c>
-      <c r="M38" s="30">
+      <c r="M38" s="31">
         <v>1.01</v>
       </c>
-      <c r="N38" s="32"/>
-      <c r="O38" s="30">
+      <c r="N38" s="33"/>
+      <c r="O38" s="31">
         <v>0.77</v>
       </c>
-      <c r="P38" s="30">
+      <c r="P38" s="31">
         <v>0.76</v>
       </c>
-      <c r="Q38" s="30">
+      <c r="Q38" s="31">
         <v>0.59</v>
       </c>
-      <c r="R38" s="30">
+      <c r="R38" s="31">
         <v>0.58</v>
       </c>
-      <c r="S38" s="30">
+      <c r="S38" s="31">
         <v>0.55</v>
       </c>
-      <c r="T38" s="30">
+      <c r="T38" s="31">
         <v>0.67</v>
       </c>
-      <c r="U38" s="30">
+      <c r="U38" s="31">
         <v>0.65</v>
       </c>
-      <c r="V38" s="30">
+      <c r="V38" s="31">
         <v>0.53</v>
       </c>
-      <c r="W38" s="30">
+      <c r="W38" s="31">
         <v>0.51</v>
       </c>
-      <c r="X38" s="30">
+      <c r="X38" s="31">
         <v>0.48</v>
       </c>
-      <c r="Y38" s="30">
+      <c r="Y38" s="31">
         <v>0.53</v>
       </c>
-      <c r="Z38" s="30">
+      <c r="Z38" s="31">
         <v>0.53</v>
       </c>
-      <c r="AA38" s="30">
+      <c r="AA38" s="31">
         <v>0.55</v>
       </c>
-      <c r="AB38" s="30">
+      <c r="AB38" s="31">
         <v>0.48</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="31">
         <v>0.39</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <v>0.39</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <v>0.4</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <v>0.41</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <v>0.44</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="31">
         <v>0.45</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="31">
         <v>0.53</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="31">
         <v>0.64</v>
       </c>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="30">
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="31">
         <v>0.66</v>
       </c>
-      <c r="P39" s="30">
+      <c r="P39" s="31">
         <v>0.64</v>
       </c>
-      <c r="Q39" s="30">
+      <c r="Q39" s="31">
         <v>0.61</v>
       </c>
-      <c r="R39" s="30">
+      <c r="R39" s="31">
         <v>0.6</v>
       </c>
-      <c r="S39" s="30">
+      <c r="S39" s="31">
         <v>0.58</v>
       </c>
-      <c r="T39" s="30">
+      <c r="T39" s="31">
         <v>0.57</v>
       </c>
-      <c r="U39" s="30">
+      <c r="U39" s="31">
         <v>0.54</v>
       </c>
-      <c r="V39" s="30">
+      <c r="V39" s="31">
         <v>0.52</v>
       </c>
-      <c r="W39" s="30">
+      <c r="W39" s="31">
         <v>0.52</v>
       </c>
-      <c r="X39" s="30">
+      <c r="X39" s="31">
         <v>0.51</v>
       </c>
-      <c r="Y39" s="32"/>
-      <c r="Z39" s="32"/>
-      <c r="AA39" s="32"/>
-      <c r="AB39" s="32"/>
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="31">
         <v>0.29</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="31">
         <v>0.41</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="31">
         <v>0.35</v>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="31">
         <v>0.47</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <v>0.55</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41" s="31">
         <v>0.25</v>
       </c>
-      <c r="H41" s="30">
+      <c r="H41" s="31">
         <v>0.47</v>
       </c>
-      <c r="I41" s="30">
+      <c r="I41" s="31">
         <v>0.36</v>
       </c>
-      <c r="J41" s="30">
+      <c r="J41" s="31">
         <v>0.64</v>
       </c>
-      <c r="K41" s="30">
+      <c r="K41" s="31">
         <v>0.58</v>
       </c>
-      <c r="L41" s="30">
+      <c r="L41" s="31">
         <v>0.72</v>
       </c>
-      <c r="M41" s="30">
+      <c r="M41" s="31">
         <v>1.06</v>
       </c>
-      <c r="N41" s="32"/>
-      <c r="O41" s="30">
+      <c r="N41" s="33"/>
+      <c r="O41" s="31">
         <v>0.8</v>
       </c>
-      <c r="P41" s="30">
+      <c r="P41" s="31">
         <v>0.79</v>
       </c>
-      <c r="Q41" s="30">
+      <c r="Q41" s="31">
         <v>0.6</v>
       </c>
-      <c r="R41" s="30">
+      <c r="R41" s="31">
         <v>0.59</v>
       </c>
-      <c r="S41" s="30">
+      <c r="S41" s="31">
         <v>0.56</v>
       </c>
-      <c r="T41" s="30">
+      <c r="T41" s="31">
         <v>0.67</v>
       </c>
-      <c r="U41" s="30">
+      <c r="U41" s="31">
         <v>0.66</v>
       </c>
-      <c r="V41" s="30">
+      <c r="V41" s="31">
         <v>0.54</v>
       </c>
-      <c r="W41" s="30">
+      <c r="W41" s="31">
         <v>0.54</v>
       </c>
-      <c r="X41" s="30">
+      <c r="X41" s="31">
         <v>0.52</v>
       </c>
-      <c r="Y41" s="30">
+      <c r="Y41" s="31">
         <v>0.62</v>
       </c>
-      <c r="Z41" s="30">
+      <c r="Z41" s="31">
         <v>0.59</v>
       </c>
-      <c r="AA41" s="30">
+      <c r="AA41" s="31">
         <v>0.6</v>
       </c>
-      <c r="AB41" s="30">
+      <c r="AB41" s="31">
         <v>0.52</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <v>0.41</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <v>0.41</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>0.42</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <v>0.42</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <v>0.46</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="31">
         <v>0.47</v>
       </c>
-      <c r="H42" s="30">
+      <c r="H42" s="31">
         <v>0.56</v>
       </c>
-      <c r="I42" s="30">
+      <c r="I42" s="31">
         <v>0.67</v>
       </c>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
-      <c r="O42" s="30">
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="31">
         <v>0.68</v>
       </c>
-      <c r="P42" s="30">
+      <c r="P42" s="31">
         <v>0.65</v>
       </c>
-      <c r="Q42" s="30">
+      <c r="Q42" s="31">
         <v>0.62</v>
       </c>
-      <c r="R42" s="30">
+      <c r="R42" s="31">
         <v>0.61</v>
       </c>
-      <c r="S42" s="30">
+      <c r="S42" s="31">
         <v>0.6</v>
       </c>
-      <c r="T42" s="30">
+      <c r="T42" s="31">
         <v>0.59</v>
       </c>
-      <c r="U42" s="30">
+      <c r="U42" s="31">
         <v>0.58</v>
       </c>
-      <c r="V42" s="30">
+      <c r="V42" s="31">
         <v>0.56</v>
       </c>
-      <c r="W42" s="30">
+      <c r="W42" s="31">
         <v>0.57</v>
       </c>
-      <c r="X42" s="30">
+      <c r="X42" s="31">
         <v>0.57</v>
       </c>
-      <c r="Y42" s="32"/>
-      <c r="Z42" s="32"/>
-      <c r="AA42" s="32"/>
-      <c r="AB42" s="32"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="27"/>
-      <c r="AA43" s="27"/>
-      <c r="AB43" s="27"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="31">
         <v>0.56</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <v>0.79</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <v>0.62</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="31">
         <v>0.98</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="31">
         <v>0.94</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="31">
         <v>0.66</v>
       </c>
-      <c r="H44" s="30">
+      <c r="H44" s="31">
         <v>0.86</v>
       </c>
-      <c r="I44" s="30">
+      <c r="I44" s="31">
         <v>0.66</v>
       </c>
-      <c r="J44" s="30">
+      <c r="J44" s="31">
         <v>1.07</v>
       </c>
-      <c r="K44" s="30">
+      <c r="K44" s="31">
         <v>1.14</v>
       </c>
-      <c r="L44" s="30">
+      <c r="L44" s="31">
         <v>1.12</v>
       </c>
-      <c r="M44" s="30">
+      <c r="M44" s="31">
         <v>1.82</v>
       </c>
-      <c r="N44" s="30">
+      <c r="N44" s="31">
         <v>2.36</v>
       </c>
-      <c r="O44" s="30">
+      <c r="O44" s="31">
         <v>1.01</v>
       </c>
-      <c r="P44" s="30">
+      <c r="P44" s="31">
         <v>0.92</v>
       </c>
-      <c r="Q44" s="30">
+      <c r="Q44" s="31">
         <v>0.75</v>
       </c>
-      <c r="R44" s="30">
+      <c r="R44" s="31">
         <v>0.95</v>
       </c>
-      <c r="S44" s="30">
+      <c r="S44" s="31">
         <v>0.82</v>
       </c>
-      <c r="T44" s="30">
+      <c r="T44" s="31">
         <v>1.09</v>
       </c>
-      <c r="U44" s="30">
+      <c r="U44" s="31">
         <v>0.92</v>
       </c>
-      <c r="V44" s="30">
+      <c r="V44" s="31">
         <v>0.86</v>
       </c>
-      <c r="W44" s="30">
+      <c r="W44" s="31">
         <v>0.87</v>
       </c>
-      <c r="X44" s="30">
+      <c r="X44" s="31">
         <v>0.95</v>
       </c>
-      <c r="Y44" s="30">
+      <c r="Y44" s="31">
         <v>1.02</v>
       </c>
-      <c r="Z44" s="30">
+      <c r="Z44" s="31">
         <v>1.09</v>
       </c>
-      <c r="AA44" s="30">
+      <c r="AA44" s="31">
         <v>1.08</v>
       </c>
-      <c r="AB44" s="30">
+      <c r="AB44" s="31">
         <v>1.02</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="29" t="s">
         <v>338</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="31">
         <v>0.78</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="31">
         <v>0.8</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="31">
         <v>0.82</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="31">
         <v>0.83</v>
       </c>
-      <c r="F45" s="30">
+      <c r="F45" s="31">
         <v>0.86</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45" s="31">
         <v>0.9</v>
       </c>
-      <c r="H45" s="30">
+      <c r="H45" s="31">
         <v>0.98</v>
       </c>
-      <c r="I45" s="30">
+      <c r="I45" s="31">
         <v>1.17</v>
       </c>
-      <c r="J45" s="30">
+      <c r="J45" s="31">
         <v>1.55</v>
       </c>
-      <c r="K45" s="30">
+      <c r="K45" s="31">
         <v>1.52</v>
       </c>
-      <c r="L45" s="30">
+      <c r="L45" s="31">
         <v>1.47</v>
       </c>
-      <c r="M45" s="30">
+      <c r="M45" s="31">
         <v>1.42</v>
       </c>
-      <c r="N45" s="30">
+      <c r="N45" s="31">
         <v>1.29</v>
       </c>
-      <c r="O45" s="30">
+      <c r="O45" s="31">
         <v>0.9</v>
       </c>
-      <c r="P45" s="30">
+      <c r="P45" s="31">
         <v>0.9</v>
       </c>
-      <c r="Q45" s="30">
+      <c r="Q45" s="31">
         <v>0.89</v>
       </c>
-      <c r="R45" s="30">
+      <c r="R45" s="31">
         <v>0.93</v>
       </c>
-      <c r="S45" s="30">
+      <c r="S45" s="31">
         <v>0.91</v>
       </c>
-      <c r="T45" s="30">
+      <c r="T45" s="31">
         <v>0.94</v>
       </c>
-      <c r="U45" s="30">
+      <c r="U45" s="31">
         <v>0.92</v>
       </c>
-      <c r="V45" s="30">
+      <c r="V45" s="31">
         <v>0.95</v>
       </c>
-      <c r="W45" s="30">
+      <c r="W45" s="31">
         <v>0.99</v>
       </c>
-      <c r="X45" s="30">
+      <c r="X45" s="31">
         <v>1.03</v>
       </c>
-      <c r="Y45" s="32"/>
-      <c r="Z45" s="32"/>
-      <c r="AA45" s="32"/>
-      <c r="AB45" s="32"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
-      <c r="AA46" s="27"/>
-      <c r="AB46" s="27"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="31">
         <v>1.95</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="31">
         <v>1.38</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="31">
         <v>12.52</v>
       </c>
-      <c r="E47" s="32"/>
-      <c r="F47" s="30">
+      <c r="E47" s="33"/>
+      <c r="F47" s="31">
         <v>0.41</v>
       </c>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="30">
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="31">
         <v>1.47</v>
       </c>
-      <c r="K47" s="30">
+      <c r="K47" s="31">
         <v>4.05</v>
       </c>
-      <c r="L47" s="30">
+      <c r="L47" s="31">
         <v>40.76</v>
       </c>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
-      <c r="O47" s="30">
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="31">
         <v>4.23</v>
       </c>
-      <c r="P47" s="30">
+      <c r="P47" s="31">
         <v>2.71</v>
       </c>
-      <c r="Q47" s="30">
+      <c r="Q47" s="31">
         <v>1.49</v>
       </c>
-      <c r="R47" s="32"/>
-      <c r="S47" s="30">
+      <c r="R47" s="33"/>
+      <c r="S47" s="31">
         <v>2.14</v>
       </c>
-      <c r="T47" s="32"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="32"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="30">
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="31">
         <v>4.38</v>
       </c>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="30">
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="31">
         <v>6.72</v>
       </c>
-      <c r="AA47" s="32"/>
-      <c r="AB47" s="30">
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="31">
         <v>2.37</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="29" t="s">
         <v>341</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="31">
         <v>1.16</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="31">
         <v>1.66</v>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="31">
         <v>2.34</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="31">
         <v>2.88</v>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="31">
         <v>1.82</v>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <v>133.54</v>
       </c>
-      <c r="H48" s="30">
+      <c r="H48" s="31">
         <v>6.29</v>
       </c>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
-      <c r="N48" s="32"/>
-      <c r="O48" s="30">
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="31">
         <v>3.01</v>
       </c>
-      <c r="P48" s="30">
+      <c r="P48" s="31">
         <v>3.92</v>
       </c>
-      <c r="Q48" s="30">
+      <c r="Q48" s="31">
         <v>6.81</v>
       </c>
-      <c r="R48" s="32"/>
-      <c r="S48" s="32"/>
-      <c r="T48" s="32"/>
-      <c r="U48" s="32"/>
-      <c r="V48" s="32"/>
-      <c r="W48" s="32"/>
-      <c r="X48" s="30">
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="31">
         <v>9.78</v>
       </c>
-      <c r="Y48" s="32"/>
-      <c r="Z48" s="32"/>
-      <c r="AA48" s="32"/>
-      <c r="AB48" s="32"/>
+      <c r="Y48" s="33"/>
+      <c r="Z48" s="33"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="27" t="s">
         <v>342</v>
       </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
-      <c r="AA49" s="27"/>
-      <c r="AB49" s="27"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
+      <c r="A50" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="B50" s="30">
+      <c r="B50" s="31">
         <v>2.99</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="31">
         <v>4.37</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="31">
         <v>2.72</v>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="31">
         <v>5.79</v>
       </c>
-      <c r="F50" s="30">
+      <c r="F50" s="31">
         <v>2.58</v>
       </c>
-      <c r="G50" s="32"/>
-      <c r="H50" s="30">
+      <c r="G50" s="33"/>
+      <c r="H50" s="31">
         <v>12.15</v>
       </c>
-      <c r="I50" s="30">
+      <c r="I50" s="31">
         <v>11.32</v>
       </c>
-      <c r="J50" s="30">
+      <c r="J50" s="31">
         <v>4.77</v>
       </c>
-      <c r="K50" s="30">
+      <c r="K50" s="31">
         <v>21.6</v>
       </c>
-      <c r="L50" s="30">
+      <c r="L50" s="31">
         <v>5.49</v>
       </c>
-      <c r="M50" s="30">
+      <c r="M50" s="31">
         <v>16.87</v>
       </c>
-      <c r="N50" s="30">
+      <c r="N50" s="31">
         <v>7.02</v>
       </c>
-      <c r="O50" s="30">
+      <c r="O50" s="31">
         <v>2.94</v>
       </c>
-      <c r="P50" s="30">
+      <c r="P50" s="31">
         <v>3.0</v>
       </c>
-      <c r="Q50" s="30">
+      <c r="Q50" s="31">
         <v>3.2</v>
       </c>
-      <c r="R50" s="30">
+      <c r="R50" s="31">
         <v>24.87</v>
       </c>
-      <c r="S50" s="30">
+      <c r="S50" s="31">
         <v>5.24</v>
       </c>
-      <c r="T50" s="30">
+      <c r="T50" s="31">
         <v>7.19</v>
       </c>
-      <c r="U50" s="30">
+      <c r="U50" s="31">
         <v>3.65</v>
       </c>
-      <c r="V50" s="30">
+      <c r="V50" s="31">
         <v>4.32</v>
       </c>
-      <c r="W50" s="30">
+      <c r="W50" s="31">
         <v>3.19</v>
       </c>
-      <c r="X50" s="30">
+      <c r="X50" s="31">
         <v>6.15</v>
       </c>
-      <c r="Y50" s="30">
+      <c r="Y50" s="31">
         <v>3.76</v>
       </c>
-      <c r="Z50" s="30">
+      <c r="Z50" s="31">
         <v>3.05</v>
       </c>
-      <c r="AA50" s="30">
+      <c r="AA50" s="31">
         <v>3.67</v>
       </c>
-      <c r="AB50" s="30">
+      <c r="AB50" s="31">
         <v>7.48</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="B51" s="30">
+      <c r="B51" s="31">
         <v>3.35</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="31">
         <v>4.06</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="31">
         <v>4.7</v>
       </c>
-      <c r="E51" s="30">
+      <c r="E51" s="31">
         <v>6.06</v>
       </c>
-      <c r="F51" s="30">
+      <c r="F51" s="31">
         <v>5.66</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51" s="31">
         <v>10.93</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="31">
         <v>7.51</v>
       </c>
-      <c r="I51" s="30">
+      <c r="I51" s="31">
         <v>8.54</v>
       </c>
-      <c r="J51" s="30">
+      <c r="J51" s="31">
         <v>7.77</v>
       </c>
-      <c r="K51" s="30">
+      <c r="K51" s="31">
         <v>6.75</v>
       </c>
-      <c r="L51" s="30">
+      <c r="L51" s="31">
         <v>5.49</v>
       </c>
-      <c r="M51" s="30">
+      <c r="M51" s="31">
         <v>5.17</v>
       </c>
-      <c r="N51" s="30">
+      <c r="N51" s="31">
         <v>4.63</v>
       </c>
-      <c r="O51" s="30">
+      <c r="O51" s="31">
         <v>3.73</v>
       </c>
-      <c r="P51" s="30">
+      <c r="P51" s="31">
         <v>4.59</v>
       </c>
-      <c r="Q51" s="30">
+      <c r="Q51" s="31">
         <v>5.1</v>
       </c>
-      <c r="R51" s="30">
+      <c r="R51" s="31">
         <v>5.61</v>
       </c>
-      <c r="S51" s="30">
+      <c r="S51" s="31">
         <v>4.41</v>
       </c>
-      <c r="T51" s="30">
+      <c r="T51" s="31">
         <v>4.47</v>
       </c>
-      <c r="U51" s="30">
+      <c r="U51" s="31">
         <v>3.95</v>
       </c>
-      <c r="V51" s="30">
+      <c r="V51" s="31">
         <v>3.81</v>
       </c>
-      <c r="W51" s="30">
+      <c r="W51" s="31">
         <v>3.69</v>
       </c>
-      <c r="X51" s="30">
+      <c r="X51" s="31">
         <v>4.18</v>
       </c>
-      <c r="Y51" s="32"/>
-      <c r="Z51" s="32"/>
-      <c r="AA51" s="32"/>
-      <c r="AB51" s="32"/>
+      <c r="Y51" s="33"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
-      <c r="AA52" s="27"/>
-      <c r="AB52" s="27"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="31">
         <v>6.7</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C53" s="31">
         <v>12.6</v>
       </c>
-      <c r="D53" s="30">
+      <c r="D53" s="31">
         <v>5.85</v>
       </c>
-      <c r="E53" s="30">
+      <c r="E53" s="31">
         <v>36.35</v>
       </c>
-      <c r="F53" s="30">
+      <c r="F53" s="31">
         <v>3.72</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="30">
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="31">
         <v>7.77</v>
       </c>
-      <c r="K53" s="32"/>
-      <c r="L53" s="30">
+      <c r="K53" s="33"/>
+      <c r="L53" s="31">
         <v>8.85</v>
       </c>
-      <c r="M53" s="30">
+      <c r="M53" s="31">
         <v>61.45</v>
       </c>
-      <c r="N53" s="30">
+      <c r="N53" s="31">
         <v>8.29</v>
       </c>
-      <c r="O53" s="30">
+      <c r="O53" s="31">
         <v>3.61</v>
       </c>
-      <c r="P53" s="30">
+      <c r="P53" s="31">
         <v>3.69</v>
       </c>
-      <c r="Q53" s="30">
+      <c r="Q53" s="31">
         <v>4.35</v>
       </c>
-      <c r="R53" s="32"/>
-      <c r="S53" s="30">
+      <c r="R53" s="33"/>
+      <c r="S53" s="31">
         <v>9.56</v>
       </c>
-      <c r="T53" s="30">
+      <c r="T53" s="31">
         <v>14.08</v>
       </c>
-      <c r="U53" s="30">
+      <c r="U53" s="31">
         <v>5.09</v>
       </c>
-      <c r="V53" s="30">
+      <c r="V53" s="31">
         <v>8.45</v>
       </c>
-      <c r="W53" s="30">
+      <c r="W53" s="31">
         <v>5.53</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>208.27</v>
       </c>
-      <c r="Y53" s="30">
+      <c r="Y53" s="31">
         <v>7.2</v>
       </c>
-      <c r="Z53" s="30">
+      <c r="Z53" s="31">
         <v>4.48</v>
       </c>
-      <c r="AA53" s="30">
+      <c r="AA53" s="31">
         <v>5.85</v>
       </c>
-      <c r="AB53" s="30">
+      <c r="AB53" s="31">
         <v>19.16</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="B54" s="30">
+      <c r="B54" s="31">
         <v>6.85</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="31">
         <v>12.74</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="31">
         <v>17.59</v>
       </c>
-      <c r="E54" s="30">
+      <c r="E54" s="31">
         <v>52.39</v>
       </c>
-      <c r="F54" s="30">
+      <c r="F54" s="31">
         <v>20.09</v>
       </c>
-      <c r="G54" s="32"/>
-      <c r="H54" s="30">
+      <c r="G54" s="33"/>
+      <c r="H54" s="31">
         <v>23.86</v>
       </c>
-      <c r="I54" s="30">
+      <c r="I54" s="31">
         <v>23.86</v>
       </c>
-      <c r="J54" s="30">
+      <c r="J54" s="31">
         <v>12.78</v>
       </c>
-      <c r="K54" s="30">
+      <c r="K54" s="31">
         <v>10.0</v>
       </c>
-      <c r="L54" s="30">
+      <c r="L54" s="31">
         <v>7.27</v>
       </c>
-      <c r="M54" s="30">
+      <c r="M54" s="31">
         <v>6.68</v>
       </c>
-      <c r="N54" s="30">
+      <c r="N54" s="31">
         <v>5.98</v>
       </c>
-      <c r="O54" s="30">
+      <c r="O54" s="31">
         <v>5.16</v>
       </c>
-      <c r="P54" s="30">
+      <c r="P54" s="31">
         <v>7.1</v>
       </c>
-      <c r="Q54" s="30">
+      <c r="Q54" s="31">
         <v>8.72</v>
       </c>
-      <c r="R54" s="30">
+      <c r="R54" s="31">
         <v>10.9</v>
       </c>
-      <c r="S54" s="30">
+      <c r="S54" s="31">
         <v>7.45</v>
       </c>
-      <c r="T54" s="30">
+      <c r="T54" s="31">
         <v>8.38</v>
       </c>
-      <c r="U54" s="30">
+      <c r="U54" s="31">
         <v>7.39</v>
       </c>
-      <c r="V54" s="30">
+      <c r="V54" s="31">
         <v>7.32</v>
       </c>
-      <c r="W54" s="30">
+      <c r="W54" s="31">
         <v>6.81</v>
       </c>
-      <c r="X54" s="30">
+      <c r="X54" s="31">
         <v>8.07</v>
       </c>
-      <c r="Y54" s="32"/>
-      <c r="Z54" s="32"/>
-      <c r="AA54" s="32"/>
-      <c r="AB54" s="32"/>
+      <c r="Y54" s="33"/>
+      <c r="Z54" s="33"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
-      <c r="AA55" s="27"/>
-      <c r="AB55" s="27"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
+      <c r="X55" s="28"/>
+      <c r="Y55" s="28"/>
+      <c r="Z55" s="28"/>
+      <c r="AA55" s="28"/>
+      <c r="AB55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="29" t="s">
         <v>349</v>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="31">
         <v>6.7</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C56" s="31">
         <v>12.6</v>
       </c>
-      <c r="D56" s="30">
+      <c r="D56" s="31">
         <v>5.85</v>
       </c>
-      <c r="E56" s="30">
+      <c r="E56" s="31">
         <v>36.35</v>
       </c>
-      <c r="F56" s="30">
+      <c r="F56" s="31">
         <v>3.72</v>
       </c>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="30">
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="31">
         <v>7.77</v>
       </c>
-      <c r="K56" s="32"/>
-      <c r="L56" s="30">
+      <c r="K56" s="33"/>
+      <c r="L56" s="31">
         <v>8.85</v>
       </c>
-      <c r="M56" s="30">
+      <c r="M56" s="31">
         <v>61.45</v>
       </c>
-      <c r="N56" s="30">
+      <c r="N56" s="31">
         <v>8.29</v>
       </c>
-      <c r="O56" s="30">
+      <c r="O56" s="31">
         <v>3.61</v>
       </c>
-      <c r="P56" s="30">
+      <c r="P56" s="31">
         <v>3.69</v>
       </c>
-      <c r="Q56" s="30">
+      <c r="Q56" s="31">
         <v>4.35</v>
       </c>
-      <c r="R56" s="32"/>
-      <c r="S56" s="30">
+      <c r="R56" s="33"/>
+      <c r="S56" s="31">
         <v>9.56</v>
       </c>
-      <c r="T56" s="30">
+      <c r="T56" s="31">
         <v>14.08</v>
       </c>
-      <c r="U56" s="30">
+      <c r="U56" s="31">
         <v>5.09</v>
       </c>
-      <c r="V56" s="30">
+      <c r="V56" s="31">
         <v>8.45</v>
       </c>
-      <c r="W56" s="30">
+      <c r="W56" s="31">
         <v>5.53</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>208.27</v>
       </c>
-      <c r="Y56" s="30">
+      <c r="Y56" s="31">
         <v>7.28</v>
       </c>
-      <c r="Z56" s="30">
+      <c r="Z56" s="31">
         <v>4.67</v>
       </c>
-      <c r="AA56" s="30">
+      <c r="AA56" s="31">
         <v>6.62</v>
       </c>
-      <c r="AB56" s="30">
+      <c r="AB56" s="31">
         <v>11.16</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="31">
         <v>0.39</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C57" s="31">
         <v>0.39</v>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="31">
         <v>0.4</v>
       </c>
-      <c r="E57" s="30">
+      <c r="E57" s="31">
         <v>0.41</v>
       </c>
-      <c r="F57" s="30">
+      <c r="F57" s="31">
         <v>0.44</v>
       </c>
-      <c r="G57" s="30">
+      <c r="G57" s="31">
         <v>0.45</v>
       </c>
-      <c r="H57" s="30">
+      <c r="H57" s="31">
         <v>0.53</v>
       </c>
-      <c r="I57" s="30">
+      <c r="I57" s="31">
         <v>0.64</v>
       </c>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
-      <c r="N57" s="32"/>
-      <c r="O57" s="30">
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="33"/>
+      <c r="N57" s="33"/>
+      <c r="O57" s="31">
         <v>0.66</v>
       </c>
-      <c r="P57" s="30">
+      <c r="P57" s="31">
         <v>0.64</v>
       </c>
-      <c r="Q57" s="30">
+      <c r="Q57" s="31">
         <v>0.61</v>
       </c>
-      <c r="R57" s="30">
+      <c r="R57" s="31">
         <v>0.6</v>
       </c>
-      <c r="S57" s="30">
+      <c r="S57" s="31">
         <v>0.58</v>
       </c>
-      <c r="T57" s="30">
+      <c r="T57" s="31">
         <v>0.57</v>
       </c>
-      <c r="U57" s="30">
+      <c r="U57" s="31">
         <v>0.54</v>
       </c>
-      <c r="V57" s="30">
+      <c r="V57" s="31">
         <v>0.52</v>
       </c>
-      <c r="W57" s="30">
+      <c r="W57" s="31">
         <v>0.52</v>
       </c>
-      <c r="X57" s="30">
+      <c r="X57" s="31">
         <v>0.51</v>
       </c>
-      <c r="Y57" s="32"/>
-      <c r="Z57" s="32"/>
-      <c r="AA57" s="32"/>
-      <c r="AB57" s="32"/>
+      <c r="Y57" s="33"/>
+      <c r="Z57" s="33"/>
+      <c r="AA57" s="33"/>
+      <c r="AB57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
+      <c r="A58" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
-      <c r="AB58" s="27"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="28"/>
+      <c r="Y58" s="28"/>
+      <c r="Z58" s="28"/>
+      <c r="AA58" s="28"/>
+      <c r="AB58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
+      <c r="A59" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="31">
         <v>0.18</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <v>-0.26</v>
       </c>
-      <c r="D59" s="30">
+      <c r="D59" s="31">
         <v>0.02</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>-0.4</v>
       </c>
-      <c r="F59" s="30">
+      <c r="F59" s="31">
         <v>0.01</v>
       </c>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="30">
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="31">
         <v>0.02</v>
       </c>
-      <c r="K59" s="32"/>
-      <c r="L59" s="30">
+      <c r="K59" s="33"/>
+      <c r="L59" s="31">
         <v>0.02</v>
       </c>
-      <c r="M59" s="33">
+      <c r="M59" s="34">
         <v>-0.67</v>
       </c>
-      <c r="N59" s="30">
+      <c r="N59" s="31">
         <v>0.63</v>
       </c>
-      <c r="O59" s="30">
+      <c r="O59" s="31">
         <v>0.16</v>
       </c>
-      <c r="P59" s="30">
+      <c r="P59" s="31">
         <v>0.05</v>
       </c>
-      <c r="Q59" s="30">
+      <c r="Q59" s="31">
         <v>0.01</v>
       </c>
-      <c r="R59" s="32"/>
-      <c r="S59" s="30">
+      <c r="R59" s="33"/>
+      <c r="S59" s="31">
         <v>0.51</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="34">
         <v>-0.22</v>
       </c>
-      <c r="U59" s="30">
+      <c r="U59" s="31">
         <v>0.04</v>
       </c>
-      <c r="V59" s="33">
+      <c r="V59" s="34">
         <v>-0.24</v>
       </c>
-      <c r="W59" s="32">
+      <c r="W59" s="33">
         <v>0.0</v>
       </c>
-      <c r="X59" s="33">
+      <c r="X59" s="34">
         <v>-2.15</v>
       </c>
-      <c r="Y59" s="33">
+      <c r="Y59" s="34">
         <v>-0.2</v>
       </c>
-      <c r="Z59" s="30">
+      <c r="Z59" s="31">
         <v>0.11</v>
       </c>
-      <c r="AA59" s="30">
+      <c r="AA59" s="31">
         <v>0.02</v>
       </c>
-      <c r="AB59" s="32"/>
+      <c r="AB59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
+      <c r="A60" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="33">
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="34">
         <v>-1.63</v>
       </c>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="33">
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="34">
         <v>-0.84</v>
       </c>
-      <c r="K60" s="32"/>
-      <c r="L60" s="33">
+      <c r="K60" s="33"/>
+      <c r="L60" s="34">
         <v>-6.64</v>
       </c>
-      <c r="M60" s="32"/>
-      <c r="N60" s="30">
+      <c r="M60" s="33"/>
+      <c r="N60" s="31">
         <v>0.14</v>
       </c>
-      <c r="O60" s="30">
+      <c r="O60" s="31">
         <v>0.12</v>
       </c>
-      <c r="P60" s="30">
+      <c r="P60" s="31">
         <v>0.56</v>
       </c>
-      <c r="Q60" s="30">
+      <c r="Q60" s="31">
         <v>0.48</v>
       </c>
-      <c r="R60" s="32"/>
-      <c r="S60" s="30">
+      <c r="R60" s="33"/>
+      <c r="S60" s="31">
         <v>0.08</v>
       </c>
-      <c r="T60" s="33">
+      <c r="T60" s="34">
         <v>-1.05</v>
       </c>
-      <c r="U60" s="30">
+      <c r="U60" s="31">
         <v>2.12</v>
       </c>
-      <c r="V60" s="33">
+      <c r="V60" s="34">
         <v>-1.22</v>
       </c>
-      <c r="W60" s="30">
+      <c r="W60" s="31">
         <v>0.19</v>
       </c>
-      <c r="X60" s="32"/>
-      <c r="Y60" s="32"/>
-      <c r="Z60" s="32"/>
-      <c r="AA60" s="32"/>
-      <c r="AB60" s="32"/>
+      <c r="X60" s="33"/>
+      <c r="Y60" s="33"/>
+      <c r="Z60" s="33"/>
+      <c r="AA60" s="33"/>
+      <c r="AB60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27"/>
-      <c r="AB61" s="27"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="28"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
+      <c r="A62" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="B62" s="33">
+      <c r="B62" s="34">
         <v>-0.65</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>-0.28</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="31">
         <v>0.11</v>
       </c>
-      <c r="E62" s="30">
+      <c r="E62" s="31">
         <v>0.27</v>
       </c>
-      <c r="F62" s="30">
+      <c r="F62" s="31">
         <v>0.23</v>
       </c>
-      <c r="G62" s="30">
+      <c r="G62" s="31">
         <v>3.33</v>
       </c>
-      <c r="H62" s="30">
+      <c r="H62" s="31">
         <v>1.65</v>
       </c>
-      <c r="I62" s="30">
+      <c r="I62" s="31">
         <v>1.38</v>
       </c>
-      <c r="J62" s="30">
+      <c r="J62" s="31">
         <v>1.42</v>
       </c>
-      <c r="K62" s="30">
+      <c r="K62" s="31">
         <v>2.38</v>
       </c>
-      <c r="L62" s="30">
+      <c r="L62" s="31">
         <v>2.18</v>
       </c>
-      <c r="M62" s="30">
+      <c r="M62" s="31">
         <v>3.0</v>
       </c>
-      <c r="N62" s="32"/>
-      <c r="O62" s="30">
+      <c r="N62" s="33"/>
+      <c r="O62" s="31">
         <v>0.47</v>
       </c>
-      <c r="P62" s="30">
+      <c r="P62" s="31">
         <v>0.56</v>
       </c>
-      <c r="Q62" s="30">
+      <c r="Q62" s="31">
         <v>0.74</v>
       </c>
-      <c r="R62" s="30">
+      <c r="R62" s="31">
         <v>1.64</v>
       </c>
-      <c r="S62" s="30">
+      <c r="S62" s="31">
         <v>1.26</v>
       </c>
-      <c r="T62" s="30">
+      <c r="T62" s="31">
         <v>1.87</v>
       </c>
-      <c r="U62" s="30">
+      <c r="U62" s="31">
         <v>1.3</v>
       </c>
-      <c r="V62" s="30">
+      <c r="V62" s="31">
         <v>1.29</v>
       </c>
-      <c r="W62" s="30">
+      <c r="W62" s="31">
         <v>1.1</v>
       </c>
-      <c r="X62" s="30">
+      <c r="X62" s="31">
         <v>0.79</v>
       </c>
-      <c r="Y62" s="30">
+      <c r="Y62" s="31">
         <v>0.95</v>
       </c>
-      <c r="Z62" s="30">
+      <c r="Z62" s="31">
         <v>0.78</v>
       </c>
-      <c r="AA62" s="30">
+      <c r="AA62" s="31">
         <v>0.85</v>
       </c>
-      <c r="AB62" s="30">
+      <c r="AB62" s="31">
         <v>0.69</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="29" t="s">
         <v>356</v>
       </c>
-      <c r="B63" s="33">
+      <c r="B63" s="34">
         <v>-0.06</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C63" s="31">
         <v>0.53</v>
       </c>
-      <c r="D63" s="30">
+      <c r="D63" s="31">
         <v>0.93</v>
       </c>
-      <c r="E63" s="30">
+      <c r="E63" s="31">
         <v>1.22</v>
       </c>
-      <c r="F63" s="30">
+      <c r="F63" s="31">
         <v>1.43</v>
       </c>
-      <c r="G63" s="30">
+      <c r="G63" s="31">
         <v>1.9</v>
       </c>
-      <c r="H63" s="30">
+      <c r="H63" s="31">
         <v>1.81</v>
       </c>
-      <c r="I63" s="30">
+      <c r="I63" s="31">
         <v>2.07</v>
       </c>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
-      <c r="M63" s="32"/>
-      <c r="N63" s="32"/>
-      <c r="O63" s="30">
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="31">
         <v>0.83</v>
       </c>
-      <c r="P63" s="30">
+      <c r="P63" s="31">
         <v>1.12</v>
       </c>
-      <c r="Q63" s="30">
+      <c r="Q63" s="31">
         <v>1.32</v>
       </c>
-      <c r="R63" s="30">
+      <c r="R63" s="31">
         <v>1.46</v>
       </c>
-      <c r="S63" s="30">
+      <c r="S63" s="31">
         <v>1.36</v>
       </c>
-      <c r="T63" s="30">
+      <c r="T63" s="31">
         <v>1.3</v>
       </c>
-      <c r="U63" s="30">
+      <c r="U63" s="31">
         <v>1.11</v>
       </c>
-      <c r="V63" s="30">
+      <c r="V63" s="31">
         <v>1.0</v>
       </c>
-      <c r="W63" s="30">
+      <c r="W63" s="31">
         <v>0.9</v>
       </c>
-      <c r="X63" s="30">
+      <c r="X63" s="31">
         <v>0.82</v>
       </c>
-      <c r="Y63" s="32"/>
-      <c r="Z63" s="32"/>
-      <c r="AA63" s="32"/>
-      <c r="AB63" s="32"/>
+      <c r="Y63" s="33"/>
+      <c r="Z63" s="33"/>
+      <c r="AA63" s="33"/>
+      <c r="AB63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
+      <c r="A64" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="27"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="28"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="28"/>
+      <c r="AA64" s="28"/>
+      <c r="AB64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
+      <c r="A65" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="B65" s="33">
+      <c r="B65" s="34">
         <v>-4.79</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>-1.77</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="31">
         <v>0.56</v>
       </c>
-      <c r="E65" s="30">
+      <c r="E65" s="31">
         <v>4.24</v>
       </c>
-      <c r="F65" s="30">
+      <c r="F65" s="31">
         <v>0.71</v>
       </c>
-      <c r="G65" s="32"/>
-      <c r="H65" s="30">
+      <c r="G65" s="33"/>
+      <c r="H65" s="31">
         <v>47.41</v>
       </c>
-      <c r="I65" s="32"/>
-      <c r="J65" s="30">
+      <c r="I65" s="33"/>
+      <c r="J65" s="31">
         <v>7.31</v>
       </c>
-      <c r="K65" s="32"/>
-      <c r="L65" s="30">
+      <c r="K65" s="33"/>
+      <c r="L65" s="31">
         <v>14.75</v>
       </c>
-      <c r="M65" s="30">
+      <c r="M65" s="31">
         <v>57.99</v>
       </c>
-      <c r="N65" s="32"/>
-      <c r="O65" s="30">
+      <c r="N65" s="33"/>
+      <c r="O65" s="31">
         <v>1.36</v>
       </c>
-      <c r="P65" s="30">
+      <c r="P65" s="31">
         <v>1.7</v>
       </c>
-      <c r="Q65" s="30">
+      <c r="Q65" s="31">
         <v>1.7</v>
       </c>
-      <c r="R65" s="30">
+      <c r="R65" s="31">
         <v>6.78</v>
       </c>
-      <c r="S65" s="30">
+      <c r="S65" s="31">
         <v>12.92</v>
       </c>
-      <c r="T65" s="30">
+      <c r="T65" s="31">
         <v>4.78</v>
       </c>
-      <c r="U65" s="30">
+      <c r="U65" s="31">
         <v>5.17</v>
       </c>
-      <c r="V65" s="30">
+      <c r="V65" s="31">
         <v>7.49</v>
       </c>
-      <c r="W65" s="30">
+      <c r="W65" s="31">
         <v>4.5</v>
       </c>
-      <c r="X65" s="30">
+      <c r="X65" s="31">
         <v>12.32</v>
       </c>
-      <c r="Y65" s="30">
+      <c r="Y65" s="31">
         <v>4.35</v>
       </c>
-      <c r="Z65" s="30">
+      <c r="Z65" s="31">
         <v>2.59</v>
       </c>
-      <c r="AA65" s="30">
+      <c r="AA65" s="31">
         <v>3.03</v>
       </c>
-      <c r="AB65" s="30">
+      <c r="AB65" s="31">
         <v>5.1</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
+      <c r="A66" s="29" t="s">
         <v>359</v>
       </c>
-      <c r="B66" s="33">
+      <c r="B66" s="34">
         <v>-0.3</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C66" s="31">
         <v>3.89</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D66" s="31">
         <v>8.44</v>
       </c>
-      <c r="E66" s="30">
+      <c r="E66" s="31">
         <v>18.17</v>
       </c>
-      <c r="F66" s="30">
+      <c r="F66" s="31">
         <v>14.61</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>123.96</v>
       </c>
-      <c r="H66" s="30">
+      <c r="H66" s="31">
         <v>23.98</v>
       </c>
-      <c r="I66" s="30">
+      <c r="I66" s="31">
         <v>26.61</v>
       </c>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
-      <c r="M66" s="32"/>
-      <c r="N66" s="32"/>
-      <c r="O66" s="30">
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
+      <c r="M66" s="33"/>
+      <c r="N66" s="33"/>
+      <c r="O66" s="31">
         <v>2.73</v>
       </c>
-      <c r="P66" s="30">
+      <c r="P66" s="31">
         <v>3.63</v>
       </c>
-      <c r="Q66" s="30">
+      <c r="Q66" s="31">
         <v>4.57</v>
       </c>
-      <c r="R66" s="30">
+      <c r="R66" s="31">
         <v>6.35</v>
       </c>
-      <c r="S66" s="30">
+      <c r="S66" s="31">
         <v>5.91</v>
       </c>
-      <c r="T66" s="30">
+      <c r="T66" s="31">
         <v>5.54</v>
       </c>
-      <c r="U66" s="30">
+      <c r="U66" s="31">
         <v>5.63</v>
       </c>
-      <c r="V66" s="30">
+      <c r="V66" s="31">
         <v>4.98</v>
       </c>
-      <c r="W66" s="30">
+      <c r="W66" s="31">
         <v>4.07</v>
       </c>
-      <c r="X66" s="30">
+      <c r="X66" s="31">
         <v>4.05</v>
       </c>
-      <c r="Y66" s="32"/>
-      <c r="Z66" s="32"/>
-      <c r="AA66" s="32"/>
-      <c r="AB66" s="32"/>
+      <c r="Y66" s="33"/>
+      <c r="Z66" s="33"/>
+      <c r="AA66" s="33"/>
+      <c r="AB66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
+      <c r="A67" s="27" t="s">
         <v>360</v>
       </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
-      <c r="AA67" s="27"/>
-      <c r="AB67" s="27"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="28"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
+      <c r="X67" s="28"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AB67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
+      <c r="A68" s="29" t="s">
         <v>361</v>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="34">
         <v>-2.16</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>-0.44</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="31">
         <v>0.9</v>
       </c>
-      <c r="E68" s="32"/>
-      <c r="F68" s="30">
+      <c r="E68" s="33"/>
+      <c r="F68" s="31">
         <v>0.1</v>
       </c>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="30">
+      <c r="G68" s="33"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="31">
         <v>1.86</v>
       </c>
-      <c r="K68" s="30">
+      <c r="K68" s="31">
         <v>6.83</v>
       </c>
-      <c r="L68" s="30">
+      <c r="L68" s="31">
         <v>15.59</v>
       </c>
-      <c r="M68" s="32"/>
-      <c r="N68" s="32"/>
-      <c r="O68" s="30">
+      <c r="M68" s="33"/>
+      <c r="N68" s="33"/>
+      <c r="O68" s="31">
         <v>1.47</v>
       </c>
-      <c r="P68" s="30">
+      <c r="P68" s="31">
         <v>1.12</v>
       </c>
-      <c r="Q68" s="30">
+      <c r="Q68" s="31">
         <v>1.38</v>
       </c>
-      <c r="R68" s="31">
+      <c r="R68" s="32">
         <v>206.93</v>
       </c>
-      <c r="S68" s="30">
+      <c r="S68" s="31">
         <v>2.55</v>
       </c>
-      <c r="T68" s="32"/>
-      <c r="U68" s="32"/>
-      <c r="V68" s="32"/>
-      <c r="W68" s="32"/>
-      <c r="X68" s="30">
+      <c r="T68" s="33"/>
+      <c r="U68" s="33"/>
+      <c r="V68" s="33"/>
+      <c r="W68" s="33"/>
+      <c r="X68" s="31">
         <v>2.55</v>
       </c>
-      <c r="Y68" s="30">
+      <c r="Y68" s="31">
         <v>16.44</v>
       </c>
-      <c r="Z68" s="30">
+      <c r="Z68" s="31">
         <v>2.8</v>
       </c>
-      <c r="AA68" s="30">
+      <c r="AA68" s="31">
         <v>18.51</v>
       </c>
-      <c r="AB68" s="30">
+      <c r="AB68" s="31">
         <v>1.14</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="B69" s="33">
+      <c r="B69" s="34">
         <v>-0.08</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C69" s="31">
         <v>0.99</v>
       </c>
-      <c r="D69" s="30">
+      <c r="D69" s="31">
         <v>2.37</v>
       </c>
-      <c r="E69" s="30">
+      <c r="E69" s="31">
         <v>3.78</v>
       </c>
-      <c r="F69" s="30">
+      <c r="F69" s="31">
         <v>2.86</v>
       </c>
-      <c r="G69" s="30">
+      <c r="G69" s="31">
         <v>41.38</v>
       </c>
-      <c r="H69" s="30">
+      <c r="H69" s="31">
         <v>8.61</v>
       </c>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="32"/>
-      <c r="N69" s="32"/>
-      <c r="O69" s="30">
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="33"/>
+      <c r="N69" s="33"/>
+      <c r="O69" s="31">
         <v>2.13</v>
       </c>
-      <c r="P69" s="30">
+      <c r="P69" s="31">
         <v>3.45</v>
       </c>
-      <c r="Q69" s="30">
+      <c r="Q69" s="31">
         <v>6.75</v>
       </c>
-      <c r="R69" s="30">
+      <c r="R69" s="31">
         <v>24.87</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="32">
         <v>786.15</v>
       </c>
-      <c r="T69" s="32"/>
-      <c r="U69" s="32"/>
-      <c r="V69" s="30">
+      <c r="T69" s="33"/>
+      <c r="U69" s="33"/>
+      <c r="V69" s="31">
         <v>31.76</v>
       </c>
-      <c r="W69" s="30">
+      <c r="W69" s="31">
         <v>15.06</v>
       </c>
-      <c r="X69" s="30">
+      <c r="X69" s="31">
         <v>3.35</v>
       </c>
-      <c r="Y69" s="32"/>
-      <c r="Z69" s="32"/>
-      <c r="AA69" s="32"/>
-      <c r="AB69" s="32"/>
+      <c r="Y69" s="33"/>
+      <c r="Z69" s="33"/>
+      <c r="AA69" s="33"/>
+      <c r="AB69" s="33"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
+      <c r="A70" s="27" t="s">
         <v>363</v>
       </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="27"/>
-      <c r="AA70" s="27"/>
-      <c r="AB70" s="27"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="28"/>
+      <c r="W70" s="28"/>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
+      <c r="A71" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="B71" s="33">
+      <c r="B71" s="34">
         <v>-2.27</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71" s="34">
         <v>-0.5</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="31">
         <v>2.15</v>
       </c>
-      <c r="E71" s="32"/>
-      <c r="F71" s="30">
+      <c r="E71" s="33"/>
+      <c r="F71" s="31">
         <v>0.1</v>
       </c>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="30">
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="31">
         <v>1.95</v>
       </c>
-      <c r="K71" s="30">
+      <c r="K71" s="31">
         <v>8.46</v>
       </c>
-      <c r="L71" s="30">
+      <c r="L71" s="31">
         <v>79.47</v>
       </c>
-      <c r="M71" s="32"/>
-      <c r="N71" s="32"/>
-      <c r="O71" s="30">
+      <c r="M71" s="33"/>
+      <c r="N71" s="33"/>
+      <c r="O71" s="31">
         <v>1.98</v>
       </c>
-      <c r="P71" s="30">
+      <c r="P71" s="31">
         <v>1.65</v>
       </c>
-      <c r="Q71" s="30">
+      <c r="Q71" s="31">
         <v>1.48</v>
       </c>
-      <c r="R71" s="32"/>
-      <c r="S71" s="30">
+      <c r="R71" s="33"/>
+      <c r="S71" s="31">
         <v>3.31</v>
       </c>
-      <c r="T71" s="32"/>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="30">
+      <c r="T71" s="33"/>
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="31">
         <v>3.62</v>
       </c>
-      <c r="Y71" s="32"/>
-      <c r="Z71" s="30">
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="31">
         <v>4.81</v>
       </c>
-      <c r="AA71" s="32"/>
-      <c r="AB71" s="30">
+      <c r="AA71" s="33"/>
+      <c r="AB71" s="31">
         <v>1.61</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="28" t="s">
+      <c r="A72" s="29" t="s">
         <v>365</v>
       </c>
-      <c r="B72" s="33">
+      <c r="B72" s="34">
         <v>-0.08</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C72" s="31">
         <v>1.1</v>
       </c>
-      <c r="D72" s="30">
+      <c r="D72" s="31">
         <v>2.67</v>
       </c>
-      <c r="E72" s="30">
+      <c r="E72" s="31">
         <v>4.23</v>
       </c>
-      <c r="F72" s="30">
+      <c r="F72" s="31">
         <v>3.04</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="32">
         <v>248.3</v>
       </c>
-      <c r="H72" s="30">
+      <c r="H72" s="31">
         <v>11.65</v>
       </c>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
-      <c r="M72" s="32"/>
-      <c r="N72" s="32"/>
-      <c r="O72" s="30">
+      <c r="I72" s="33"/>
+      <c r="J72" s="33"/>
+      <c r="K72" s="33"/>
+      <c r="L72" s="33"/>
+      <c r="M72" s="33"/>
+      <c r="N72" s="33"/>
+      <c r="O72" s="31">
         <v>2.8</v>
       </c>
-      <c r="P72" s="30">
+      <c r="P72" s="31">
         <v>4.88</v>
       </c>
-      <c r="Q72" s="30">
+      <c r="Q72" s="31">
         <v>10.04</v>
       </c>
-      <c r="R72" s="32"/>
-      <c r="S72" s="32"/>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="30">
+      <c r="R72" s="33"/>
+      <c r="S72" s="33"/>
+      <c r="T72" s="33"/>
+      <c r="U72" s="33"/>
+      <c r="V72" s="33"/>
+      <c r="W72" s="33"/>
+      <c r="X72" s="31">
         <v>7.76</v>
       </c>
-      <c r="Y72" s="32"/>
-      <c r="Z72" s="32"/>
-      <c r="AA72" s="32"/>
-      <c r="AB72" s="32"/>
+      <c r="Y72" s="33"/>
+      <c r="Z72" s="33"/>
+      <c r="AA72" s="33"/>
+      <c r="AB72" s="33"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
